--- a/sofiback/public/uploads/Nuevo Hoja de cálculo de Microsoft Excel.xlsx
+++ b/sofiback/public/uploads/Nuevo Hoja de cálculo de Microsoft Excel.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$H$248</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -19,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="282">
   <si>
     <t>Cod. Producto</t>
   </si>
@@ -144,9 +147,6 @@
     <t>CHORIZO DE RES AL VACIO DE 1 KG</t>
   </si>
   <si>
-    <t>CHORIZO DE RES PICANTE AL VACIO DE 1 KG</t>
-  </si>
-  <si>
     <t>CHORIZO ESPAÑOL AL VACIO DE 200 GRS.</t>
   </si>
   <si>
@@ -366,9 +366,6 @@
     <t>MORTADELA JAMONADA FAMILIAR JUMBO EN BARRA</t>
   </si>
   <si>
-    <t>MORTADELA JAMONADA JUMBO EN BARRA</t>
-  </si>
-  <si>
     <t>MORTADELA PRIMAVERA EN BARRA DE 3.8 KG</t>
   </si>
   <si>
@@ -555,9 +552,6 @@
     <t>P.U. HUEVO MARRON MAPLE 30 4TA LB</t>
   </si>
   <si>
-    <t>P.U. HUEVO MARRON MAPLE 30 EXTRA LB</t>
-  </si>
-  <si>
     <t>P.U. MERMELADA DE DURAZNO 500GRS</t>
   </si>
   <si>
@@ -793,9 +787,6 @@
   </si>
   <si>
     <t>RECIPIENTE FELINO GATITO 900 GRS</t>
-  </si>
-  <si>
-    <t>SALAME EN BARRA AL VACIO DE 300 GRS.</t>
   </si>
   <si>
     <t>SALAME FETEADO AL VACIO DE 100 GR.</t>
@@ -883,7 +874,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="######0"/>
+    <numFmt numFmtId="165" formatCode="######0.00"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -891,13 +886,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="63"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -927,9 +935,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1210,32 +1223,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H252"/>
+  <dimension ref="A1:H248"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.21875" customWidth="1"/>
+    <col min="2" max="2" width="49.109375" customWidth="1"/>
+    <col min="5" max="5" width="9.5546875" style="3" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1252,7 +1270,7 @@
       <c r="D2" s="1">
         <v>1005.9</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="2">
         <v>46231.805069444446</v>
       </c>
       <c r="F2" s="1">
@@ -1278,7 +1296,7 @@
       <c r="D3" s="1">
         <v>8.25</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="2">
         <v>46218.624479166669</v>
       </c>
       <c r="F3" s="1">
@@ -1304,7 +1322,7 @@
       <c r="D4" s="1">
         <v>12.55</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="2">
         <v>46218.624479166669</v>
       </c>
       <c r="F4" s="1">
@@ -1330,7 +1348,7 @@
       <c r="D5" s="1">
         <v>91</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="2">
         <v>46230.403055555558</v>
       </c>
       <c r="F5" s="1">
@@ -1356,7 +1374,7 @@
       <c r="D6" s="1">
         <v>50</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="2">
         <v>46168.649386574078</v>
       </c>
       <c r="F6" s="1">
@@ -1382,7 +1400,7 @@
       <c r="D7" s="1">
         <v>33</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="2">
         <v>46202.447824074072</v>
       </c>
       <c r="F7" s="1">
@@ -1408,7 +1426,7 @@
       <c r="D8" s="1">
         <v>44</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="2">
         <v>46202.447824074072</v>
       </c>
       <c r="F8" s="1">
@@ -1434,7 +1452,7 @@
       <c r="D9" s="1">
         <v>10.9</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="2">
         <v>46203.685613425929</v>
       </c>
       <c r="F9" s="1">
@@ -1460,7 +1478,7 @@
       <c r="D10" s="1">
         <v>10.3</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="2">
         <v>46202.447824074072</v>
       </c>
       <c r="F10" s="1">
@@ -1486,7 +1504,7 @@
       <c r="D11" s="1">
         <v>5.76</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="2">
         <v>46234.612314814818</v>
       </c>
       <c r="F11" s="1">
@@ -1512,7 +1530,7 @@
       <c r="D12" s="1">
         <v>47</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="2">
         <v>46234.606469907405</v>
       </c>
       <c r="F12" s="1">
@@ -1538,7 +1556,7 @@
       <c r="D13" s="1">
         <v>100</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="2">
         <v>46234.387870370374</v>
       </c>
       <c r="F13" s="1">
@@ -1564,7 +1582,7 @@
       <c r="D14" s="1">
         <v>15</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="2">
         <v>46234.387870370374</v>
       </c>
       <c r="F14" s="1">
@@ -1590,7 +1608,7 @@
       <c r="D15" s="1">
         <v>317</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="2">
         <v>46225.565937500003</v>
       </c>
       <c r="F15" s="1">
@@ -1616,7 +1634,7 @@
       <c r="D16" s="1">
         <v>306</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="2">
         <v>46181.741770833331</v>
       </c>
       <c r="F16" s="1">
@@ -1642,7 +1660,7 @@
       <c r="D17" s="1">
         <v>0.3</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="2">
         <v>46218.528634259259</v>
       </c>
       <c r="F17" s="1">
@@ -1668,7 +1686,7 @@
       <c r="D18" s="1">
         <v>0.2</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="2">
         <v>46168.649386574078</v>
       </c>
       <c r="F18" s="1">
@@ -1694,7 +1712,7 @@
       <c r="D19" s="1">
         <v>3</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="2">
         <v>46168.649386574078</v>
       </c>
       <c r="F19" s="1">
@@ -1720,7 +1738,7 @@
       <c r="D20" s="1">
         <v>0.25</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="2">
         <v>46234.593993055554</v>
       </c>
       <c r="F20" s="1">
@@ -1746,7 +1764,7 @@
       <c r="D21" s="1">
         <v>175.95</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" s="2">
         <v>46234.593993055554</v>
       </c>
       <c r="F21" s="1">
@@ -1772,7 +1790,7 @@
       <c r="D22" s="1">
         <v>266</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" s="2">
         <v>46193.459548611114</v>
       </c>
       <c r="F22" s="1">
@@ -1798,7 +1816,7 @@
       <c r="D23" s="1">
         <v>3</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" s="2">
         <v>46234.593993055554</v>
       </c>
       <c r="F23" s="1">
@@ -1824,7 +1842,7 @@
       <c r="D24" s="1">
         <v>36.549999999999997</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" s="2">
         <v>46211.435567129629</v>
       </c>
       <c r="F24" s="1">
@@ -1850,7 +1868,7 @@
       <c r="D25" s="1">
         <v>42.5</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" s="2">
         <v>46225.540694444448</v>
       </c>
       <c r="F25" s="1">
@@ -1865,7 +1883,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <v>533331</v>
+        <v>523301</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>41</v>
@@ -1874,13 +1892,13 @@
         <v>0</v>
       </c>
       <c r="D26" s="1">
-        <v>-2</v>
-      </c>
-      <c r="E26" s="1">
-        <v>46225.526608796295</v>
+        <v>0.15</v>
+      </c>
+      <c r="E26" s="2">
+        <v>46234.593993055554</v>
       </c>
       <c r="F26" s="1">
-        <v>46225</v>
+        <v>46234</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>35</v>
@@ -1891,7 +1909,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <v>523301</v>
+        <v>533000</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>42</v>
@@ -1900,10 +1918,10 @@
         <v>0</v>
       </c>
       <c r="D27" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="E27" s="1">
-        <v>46234.593993055554</v>
+        <v>0.6</v>
+      </c>
+      <c r="E27" s="2">
+        <v>46234.621759259258</v>
       </c>
       <c r="F27" s="1">
         <v>46234</v>
@@ -1917,7 +1935,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <v>533000</v>
+        <v>533328</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>43</v>
@@ -1926,9 +1944,9 @@
         <v>0</v>
       </c>
       <c r="D28" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="E28" s="1">
+        <v>58</v>
+      </c>
+      <c r="E28" s="2">
         <v>46234.621759259258</v>
       </c>
       <c r="F28" s="1">
@@ -1943,7 +1961,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <v>533328</v>
+        <v>533027</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>44</v>
@@ -1952,13 +1970,13 @@
         <v>0</v>
       </c>
       <c r="D29" s="1">
-        <v>58</v>
-      </c>
-      <c r="E29" s="1">
-        <v>46234.621759259258</v>
+        <v>4.95</v>
+      </c>
+      <c r="E29" s="2">
+        <v>46225.526608796295</v>
       </c>
       <c r="F29" s="1">
-        <v>46234</v>
+        <v>46225</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>35</v>
@@ -1969,7 +1987,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <v>533027</v>
+        <v>533030</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>45</v>
@@ -1978,13 +1996,13 @@
         <v>0</v>
       </c>
       <c r="D30" s="1">
-        <v>4.95</v>
-      </c>
-      <c r="E30" s="1">
-        <v>46225.526608796295</v>
+        <v>60.4</v>
+      </c>
+      <c r="E30" s="2">
+        <v>46218.53564814815</v>
       </c>
       <c r="F30" s="1">
-        <v>46225</v>
+        <v>46218</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>35</v>
@@ -1995,7 +2013,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <v>533030</v>
+        <v>503962</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>46</v>
@@ -2004,42 +2022,42 @@
         <v>0</v>
       </c>
       <c r="D31" s="1">
-        <v>60.4</v>
-      </c>
-      <c r="E31" s="1">
-        <v>46218.53564814815</v>
+        <v>7.4</v>
+      </c>
+      <c r="E31" s="2">
+        <v>46207.905798611115</v>
       </c>
       <c r="F31" s="1">
-        <v>46218</v>
+        <v>46207</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <v>503962</v>
+        <v>512349</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C32" s="1">
         <v>0</v>
       </c>
       <c r="D32" s="1">
-        <v>7.4</v>
-      </c>
-      <c r="E32" s="1">
-        <v>46207.905798611115</v>
+        <v>218.65</v>
+      </c>
+      <c r="E32" s="2">
+        <v>46225.526608796295</v>
       </c>
       <c r="F32" s="1">
-        <v>46207</v>
+        <v>46225</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>10</v>
@@ -2047,7 +2065,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <v>512349</v>
+        <v>503605</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>49</v>
@@ -2056,13 +2074,13 @@
         <v>0</v>
       </c>
       <c r="D33" s="1">
-        <v>218.65</v>
-      </c>
-      <c r="E33" s="1">
-        <v>46225.526608796295</v>
+        <v>34.65</v>
+      </c>
+      <c r="E33" s="2">
+        <v>46234.612314814818</v>
       </c>
       <c r="F33" s="1">
-        <v>46225</v>
+        <v>46234</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>35</v>
@@ -2073,7 +2091,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <v>503605</v>
+        <v>100003</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>50</v>
@@ -2082,16 +2100,16 @@
         <v>0</v>
       </c>
       <c r="D34" s="1">
-        <v>34.65</v>
-      </c>
-      <c r="E34" s="1">
-        <v>46234.612314814818</v>
+        <v>3092.36</v>
+      </c>
+      <c r="E34" s="2">
+        <v>46218.585393518515</v>
       </c>
       <c r="F34" s="1">
-        <v>46234</v>
+        <v>46218</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>10</v>
@@ -2099,59 +2117,59 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
-        <v>100003</v>
+        <v>521516</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C35" s="1">
         <v>0</v>
       </c>
       <c r="D35" s="1">
-        <v>3092.36</v>
-      </c>
-      <c r="E35" s="1">
-        <v>46218.585393518515</v>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E35" s="2">
+        <v>46207.905798611115</v>
       </c>
       <c r="F35" s="1">
-        <v>46218</v>
+        <v>46207</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
-        <v>521516</v>
+        <v>512395</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" s="1">
+        <v>0</v>
+      </c>
+      <c r="D36" s="1">
+        <v>7.75</v>
+      </c>
+      <c r="E36" s="2">
+        <v>46224.486076388886</v>
+      </c>
+      <c r="F36" s="1">
+        <v>46224</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C36" s="1">
-        <v>0</v>
-      </c>
-      <c r="D36" s="1">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E36" s="1">
-        <v>46207.905798611115</v>
-      </c>
-      <c r="F36" s="1">
-        <v>46207</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="H36" s="1" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
-        <v>512395</v>
+        <v>501642</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>55</v>
@@ -2160,42 +2178,42 @@
         <v>0</v>
       </c>
       <c r="D37" s="1">
-        <v>7.75</v>
-      </c>
-      <c r="E37" s="1">
+        <v>61</v>
+      </c>
+      <c r="E37" s="2">
         <v>46224.486076388886</v>
       </c>
       <c r="F37" s="1">
         <v>46224</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
-        <v>501642</v>
+        <v>501643</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C38" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D38" s="1">
-        <v>61</v>
-      </c>
-      <c r="E38" s="1">
-        <v>46224.486076388886</v>
+        <v>62</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46207.905798611115</v>
       </c>
       <c r="F38" s="1">
-        <v>46224</v>
+        <v>46207</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>14</v>
@@ -2203,33 +2221,33 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
-        <v>501643</v>
+        <v>520001</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C39" s="1">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D39" s="1">
-        <v>62</v>
-      </c>
-      <c r="E39" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="E39" s="2">
         <v>46207.905798611115</v>
       </c>
       <c r="F39" s="1">
         <v>46207</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
-        <v>520001</v>
+        <v>510362</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>58</v>
@@ -2238,24 +2256,24 @@
         <v>0</v>
       </c>
       <c r="D40" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="E40" s="1">
-        <v>46207.905798611115</v>
+        <v>3.2</v>
+      </c>
+      <c r="E40" s="2">
+        <v>46168.649386574078</v>
       </c>
       <c r="F40" s="1">
-        <v>46207</v>
+        <v>46168</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
-        <v>510362</v>
+        <v>141204</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>59</v>
@@ -2264,16 +2282,16 @@
         <v>0</v>
       </c>
       <c r="D41" s="1">
-        <v>3.2</v>
-      </c>
-      <c r="E41" s="1">
-        <v>46168.649386574078</v>
+        <v>7</v>
+      </c>
+      <c r="E41" s="2">
+        <v>46224.710949074077</v>
       </c>
       <c r="F41" s="1">
-        <v>46168</v>
+        <v>46224</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>14</v>
@@ -2281,25 +2299,25 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
-        <v>141204</v>
+        <v>141201</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C42" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D42" s="1">
-        <v>7</v>
-      </c>
-      <c r="E42" s="1">
-        <v>46224.710949074077</v>
+        <v>47</v>
+      </c>
+      <c r="E42" s="2">
+        <v>46224.713634259257</v>
       </c>
       <c r="F42" s="1">
         <v>46224</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>14</v>
@@ -2307,25 +2325,25 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
-        <v>141201</v>
+        <v>141912</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C43" s="1">
+        <v>0</v>
+      </c>
+      <c r="D43" s="1">
+        <v>6</v>
+      </c>
+      <c r="E43" s="2">
+        <v>46168.649386574078</v>
+      </c>
+      <c r="F43" s="1">
+        <v>46168</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="C43" s="1">
-        <v>12</v>
-      </c>
-      <c r="D43" s="1">
-        <v>47</v>
-      </c>
-      <c r="E43" s="1">
-        <v>46224.713634259257</v>
-      </c>
-      <c r="F43" s="1">
-        <v>46224</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>14</v>
@@ -2333,7 +2351,7 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
-        <v>141912</v>
+        <v>141202</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>63</v>
@@ -2342,16 +2360,16 @@
         <v>0</v>
       </c>
       <c r="D44" s="1">
-        <v>6</v>
-      </c>
-      <c r="E44" s="1">
-        <v>46168.649386574078</v>
+        <v>44</v>
+      </c>
+      <c r="E44" s="2">
+        <v>46207.908692129633</v>
       </c>
       <c r="F44" s="1">
-        <v>46168</v>
+        <v>46207</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>14</v>
@@ -2359,7 +2377,7 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
-        <v>141202</v>
+        <v>510300</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>64</v>
@@ -2368,24 +2386,24 @@
         <v>0</v>
       </c>
       <c r="D45" s="1">
-        <v>44</v>
-      </c>
-      <c r="E45" s="1">
-        <v>46207.908692129633</v>
+        <v>11.15</v>
+      </c>
+      <c r="E45" s="2">
+        <v>46224.713634259257</v>
       </c>
       <c r="F45" s="1">
-        <v>46207</v>
+        <v>46224</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
-        <v>510300</v>
+        <v>141203</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>65</v>
@@ -2394,24 +2412,24 @@
         <v>0</v>
       </c>
       <c r="D46" s="1">
-        <v>11.15</v>
-      </c>
-      <c r="E46" s="1">
-        <v>46224.713634259257</v>
+        <v>12</v>
+      </c>
+      <c r="E46" s="2">
+        <v>46168.649386574078</v>
       </c>
       <c r="F46" s="1">
-        <v>46224</v>
+        <v>46168</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
-        <v>141203</v>
+        <v>510001</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>66</v>
@@ -2420,24 +2438,24 @@
         <v>0</v>
       </c>
       <c r="D47" s="1">
-        <v>12</v>
-      </c>
-      <c r="E47" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="E47" s="2">
         <v>46168.649386574078</v>
       </c>
       <c r="F47" s="1">
         <v>46168</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
-        <v>510001</v>
+        <v>542039</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>67</v>
@@ -2446,24 +2464,24 @@
         <v>0</v>
       </c>
       <c r="D48" s="1">
-        <v>3.8</v>
-      </c>
-      <c r="E48" s="1">
-        <v>46168.649386574078</v>
+        <v>49</v>
+      </c>
+      <c r="E48" s="2">
+        <v>46224.478518518517</v>
       </c>
       <c r="F48" s="1">
-        <v>46168</v>
+        <v>46224</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
-        <v>542039</v>
+        <v>542037</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>68</v>
@@ -2472,16 +2490,16 @@
         <v>0</v>
       </c>
       <c r="D49" s="1">
-        <v>49</v>
-      </c>
-      <c r="E49" s="1">
+        <v>58</v>
+      </c>
+      <c r="E49" s="2">
         <v>46224.478518518517</v>
       </c>
       <c r="F49" s="1">
         <v>46224</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>14</v>
@@ -2489,7 +2507,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
-        <v>542037</v>
+        <v>542038</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>69</v>
@@ -2498,16 +2516,16 @@
         <v>0</v>
       </c>
       <c r="D50" s="1">
-        <v>58</v>
-      </c>
-      <c r="E50" s="1">
+        <v>69</v>
+      </c>
+      <c r="E50" s="2">
         <v>46224.478518518517</v>
       </c>
       <c r="F50" s="1">
         <v>46224</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>14</v>
@@ -2515,7 +2533,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
-        <v>542038</v>
+        <v>540012</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>70</v>
@@ -2524,16 +2542,16 @@
         <v>0</v>
       </c>
       <c r="D51" s="1">
-        <v>69</v>
-      </c>
-      <c r="E51" s="1">
-        <v>46224.478518518517</v>
+        <v>437</v>
+      </c>
+      <c r="E51" s="2">
+        <v>46168.649386574078</v>
       </c>
       <c r="F51" s="1">
-        <v>46224</v>
+        <v>46168</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>14</v>
@@ -2541,7 +2559,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
-        <v>540012</v>
+        <v>141309</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>71</v>
@@ -2550,16 +2568,16 @@
         <v>0</v>
       </c>
       <c r="D52" s="1">
-        <v>437</v>
-      </c>
-      <c r="E52" s="1">
-        <v>46168.649386574078</v>
+        <v>10</v>
+      </c>
+      <c r="E52" s="2">
+        <v>46224.486076388886</v>
       </c>
       <c r="F52" s="1">
-        <v>46168</v>
+        <v>46224</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>14</v>
@@ -2567,7 +2585,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
-        <v>141309</v>
+        <v>141303</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>72</v>
@@ -2576,16 +2594,16 @@
         <v>0</v>
       </c>
       <c r="D53" s="1">
-        <v>10</v>
-      </c>
-      <c r="E53" s="1">
-        <v>46224.486076388886</v>
+        <v>2</v>
+      </c>
+      <c r="E53" s="2">
+        <v>46168.649386574078</v>
       </c>
       <c r="F53" s="1">
-        <v>46224</v>
+        <v>46168</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>14</v>
@@ -2593,7 +2611,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
-        <v>141303</v>
+        <v>531502</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>73</v>
@@ -2602,42 +2620,42 @@
         <v>0</v>
       </c>
       <c r="D54" s="1">
-        <v>2</v>
-      </c>
-      <c r="E54" s="1">
-        <v>46168.649386574078</v>
+        <v>21.65</v>
+      </c>
+      <c r="E54" s="2">
+        <v>46203.745405092595</v>
       </c>
       <c r="F54" s="1">
-        <v>46168</v>
+        <v>46203</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
-        <v>531502</v>
+        <v>531505</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C55" s="1">
         <v>0</v>
       </c>
       <c r="D55" s="1">
-        <v>21.65</v>
-      </c>
-      <c r="E55" s="1">
+        <v>44.65</v>
+      </c>
+      <c r="E55" s="2">
         <v>46203.745405092595</v>
       </c>
       <c r="F55" s="1">
         <v>46203</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>31</v>
@@ -2645,7 +2663,7 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
-        <v>531505</v>
+        <v>531500</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>76</v>
@@ -2654,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="D56" s="1">
-        <v>44.65</v>
-      </c>
-      <c r="E56" s="1">
-        <v>46203.745405092595</v>
+        <v>22.5</v>
+      </c>
+      <c r="E56" s="2">
+        <v>46168.65662037037</v>
       </c>
       <c r="F56" s="1">
-        <v>46203</v>
+        <v>46168</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>31</v>
@@ -2671,7 +2689,7 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
-        <v>531500</v>
+        <v>531521</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>77</v>
@@ -2680,16 +2698,16 @@
         <v>0</v>
       </c>
       <c r="D57" s="1">
-        <v>22.5</v>
-      </c>
-      <c r="E57" s="1">
-        <v>46168.65662037037</v>
+        <v>338.24200000000002</v>
+      </c>
+      <c r="E57" s="2">
+        <v>46195.890023148146</v>
       </c>
       <c r="F57" s="1">
-        <v>46168</v>
+        <v>46195</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>31</v>
@@ -2697,25 +2715,25 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
-        <v>531521</v>
+        <v>531516</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C58" s="1">
         <v>0</v>
       </c>
       <c r="D58" s="1">
-        <v>338.24200000000002</v>
-      </c>
-      <c r="E58" s="1">
-        <v>46195.890023148146</v>
+        <v>4.62</v>
+      </c>
+      <c r="E58" s="2">
+        <v>46237.360995370371</v>
       </c>
       <c r="F58" s="1">
-        <v>46195</v>
+        <v>46237</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>31</v>
@@ -2723,7 +2741,7 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
-        <v>531516</v>
+        <v>531501</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>80</v>
@@ -2732,16 +2750,16 @@
         <v>0</v>
       </c>
       <c r="D59" s="1">
-        <v>4.62</v>
-      </c>
-      <c r="E59" s="1">
-        <v>46237.360995370371</v>
+        <v>18.71</v>
+      </c>
+      <c r="E59" s="2">
+        <v>46234.387870370374</v>
       </c>
       <c r="F59" s="1">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>31</v>
@@ -2749,129 +2767,129 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
-        <v>531501</v>
+        <v>141403</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C60" s="1">
-        <v>0</v>
+        <v>-708</v>
       </c>
       <c r="D60" s="1">
-        <v>18.71</v>
-      </c>
-      <c r="E60" s="1">
-        <v>46234.387870370374</v>
+        <v>60</v>
+      </c>
+      <c r="E60" s="2">
+        <v>46234.623784722222</v>
       </c>
       <c r="F60" s="1">
         <v>46234</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
-        <v>141403</v>
+        <v>141401</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C61" s="1">
+        <v>-711</v>
+      </c>
+      <c r="D61" s="1">
+        <v>62</v>
+      </c>
+      <c r="E61" s="2">
+        <v>46234.605046296296</v>
+      </c>
+      <c r="F61" s="1">
+        <v>46234</v>
+      </c>
+      <c r="G61" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C61" s="1">
-        <v>-708</v>
-      </c>
-      <c r="D61" s="1">
-        <v>60</v>
-      </c>
-      <c r="E61" s="1">
-        <v>46234.623784722222</v>
-      </c>
-      <c r="F61" s="1">
-        <v>46234</v>
-      </c>
-      <c r="G61" s="1" t="s">
+      <c r="H61" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
-        <v>141401</v>
+        <v>141402</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C62" s="1">
-        <v>-711</v>
+        <v>0</v>
       </c>
       <c r="D62" s="1">
-        <v>62</v>
-      </c>
-      <c r="E62" s="1">
-        <v>46234.605046296296</v>
+        <v>30</v>
+      </c>
+      <c r="E62" s="2">
+        <v>46234.387870370374</v>
       </c>
       <c r="F62" s="1">
         <v>46234</v>
       </c>
       <c r="G62" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H62" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
-        <v>141402</v>
+        <v>503906</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C63" s="1">
-        <v>0</v>
+        <v>-195</v>
       </c>
       <c r="D63" s="1">
-        <v>30</v>
-      </c>
-      <c r="E63" s="1">
-        <v>46234.387870370374</v>
+        <v>1.68</v>
+      </c>
+      <c r="E63" s="2">
+        <v>46234.623784722222</v>
       </c>
       <c r="F63" s="1">
         <v>46234</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
-        <v>503906</v>
+        <v>511221</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C64" s="1">
-        <v>-195</v>
+        <v>-37</v>
       </c>
       <c r="D64" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="E64" s="1">
-        <v>46234.623784722222</v>
+        <v>7.95</v>
+      </c>
+      <c r="E64" s="2">
+        <v>46225.524212962962</v>
       </c>
       <c r="F64" s="1">
-        <v>46234</v>
+        <v>46225</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>10</v>
@@ -2879,25 +2897,25 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
-        <v>511221</v>
+        <v>511227</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>89</v>
       </c>
       <c r="C65" s="1">
-        <v>-37</v>
+        <v>-269</v>
       </c>
       <c r="D65" s="1">
-        <v>7.95</v>
-      </c>
-      <c r="E65" s="1">
-        <v>46225.524212962962</v>
+        <v>11.2</v>
+      </c>
+      <c r="E65" s="2">
+        <v>46235.372824074075</v>
       </c>
       <c r="F65" s="1">
-        <v>46225</v>
+        <v>46235</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>10</v>
@@ -2905,77 +2923,77 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
-        <v>511227</v>
+        <v>541628</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C66" s="1">
-        <v>-269</v>
+        <v>0</v>
       </c>
       <c r="D66" s="1">
-        <v>11.2</v>
-      </c>
-      <c r="E66" s="1">
-        <v>46235.372824074075</v>
+        <v>36</v>
+      </c>
+      <c r="E66" s="2">
+        <v>46231.811585648145</v>
       </c>
       <c r="F66" s="1">
-        <v>46235</v>
+        <v>46231</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
-        <v>541628</v>
+        <v>534505</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C67" s="1">
-        <v>0</v>
+        <v>-1941</v>
       </c>
       <c r="D67" s="1">
-        <v>36</v>
-      </c>
-      <c r="E67" s="1">
-        <v>46231.811585648145</v>
+        <v>1</v>
+      </c>
+      <c r="E67" s="2">
+        <v>46237.368611111109</v>
       </c>
       <c r="F67" s="1">
-        <v>46231</v>
+        <v>46237</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
-        <v>534505</v>
+        <v>534556</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C68" s="1">
-        <v>-1941</v>
+        <v>-14282</v>
       </c>
       <c r="D68" s="1">
-        <v>1</v>
-      </c>
-      <c r="E68" s="1">
-        <v>46237.368611111109</v>
+        <v>99</v>
+      </c>
+      <c r="E68" s="2">
+        <v>46237.175104166665</v>
       </c>
       <c r="F68" s="1">
         <v>46237</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>31</v>
@@ -2983,25 +3001,25 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
-        <v>534556</v>
+        <v>534557</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>96</v>
       </c>
       <c r="C69" s="1">
-        <v>-14282</v>
+        <v>0</v>
       </c>
       <c r="D69" s="1">
-        <v>99</v>
-      </c>
-      <c r="E69" s="1">
-        <v>46237.175104166665</v>
+        <v>62</v>
+      </c>
+      <c r="E69" s="2">
+        <v>46231.996539351851</v>
       </c>
       <c r="F69" s="1">
-        <v>46237</v>
+        <v>46231</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>31</v>
@@ -3009,51 +3027,51 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
-        <v>534557</v>
+        <v>830008</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>97</v>
       </c>
       <c r="C70" s="1">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="D70" s="1">
-        <v>62</v>
-      </c>
-      <c r="E70" s="1">
-        <v>46231.996539351851</v>
+        <v>20</v>
+      </c>
+      <c r="E70" s="2">
+        <v>46233.946585648147</v>
       </c>
       <c r="F70" s="1">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
-        <v>830008</v>
+        <v>830005</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C71" s="1">
-        <v>-40</v>
+        <v>-1934</v>
       </c>
       <c r="D71" s="1">
-        <v>20</v>
-      </c>
-      <c r="E71" s="1">
-        <v>46233.946585648147</v>
+        <v>4</v>
+      </c>
+      <c r="E71" s="2">
+        <v>46232.159317129626</v>
       </c>
       <c r="F71" s="1">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>14</v>
@@ -3061,77 +3079,77 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
-        <v>830005</v>
+        <v>141920</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C72" s="1">
-        <v>-1934</v>
+        <v>-3138</v>
       </c>
       <c r="D72" s="1">
-        <v>4</v>
-      </c>
-      <c r="E72" s="1">
-        <v>46232.159317129626</v>
+        <v>15.5</v>
+      </c>
+      <c r="E72" s="2">
+        <v>46232.14707175926</v>
       </c>
       <c r="F72" s="1">
         <v>46232</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
-        <v>141920</v>
+        <v>830004</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>100</v>
       </c>
       <c r="C73" s="1">
-        <v>-3138</v>
+        <v>-124</v>
       </c>
       <c r="D73" s="1">
-        <v>15.5</v>
-      </c>
-      <c r="E73" s="1">
-        <v>46232.14707175926</v>
+        <v>20</v>
+      </c>
+      <c r="E73" s="2">
+        <v>46233.246168981481</v>
       </c>
       <c r="F73" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
-        <v>830004</v>
+        <v>830003</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>101</v>
       </c>
       <c r="C74" s="1">
-        <v>-124</v>
+        <v>0</v>
       </c>
       <c r="D74" s="1">
-        <v>20</v>
-      </c>
-      <c r="E74" s="1">
-        <v>46233.246168981481</v>
+        <v>15</v>
+      </c>
+      <c r="E74" s="2">
+        <v>46234.604432870372</v>
       </c>
       <c r="F74" s="1">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>14</v>
@@ -3139,25 +3157,25 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
-        <v>830003</v>
+        <v>830006</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C75" s="1">
         <v>0</v>
       </c>
       <c r="D75" s="1">
-        <v>15</v>
-      </c>
-      <c r="E75" s="1">
-        <v>46234.604432870372</v>
+        <v>20</v>
+      </c>
+      <c r="E75" s="2">
+        <v>46190.456006944441</v>
       </c>
       <c r="F75" s="1">
-        <v>46234</v>
+        <v>46190</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>14</v>
@@ -3165,7 +3183,7 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
-        <v>830006</v>
+        <v>830009</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>104</v>
@@ -3174,16 +3192,16 @@
         <v>0</v>
       </c>
       <c r="D76" s="1">
-        <v>20</v>
-      </c>
-      <c r="E76" s="1">
-        <v>46190.456006944441</v>
+        <v>5</v>
+      </c>
+      <c r="E76" s="2">
+        <v>46190.457685185182</v>
       </c>
       <c r="F76" s="1">
         <v>46190</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>14</v>
@@ -3191,7 +3209,7 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
-        <v>830009</v>
+        <v>530025</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>105</v>
@@ -3200,24 +3218,24 @@
         <v>0</v>
       </c>
       <c r="D77" s="1">
-        <v>5</v>
-      </c>
-      <c r="E77" s="1">
-        <v>46190.457685185182</v>
+        <v>269</v>
+      </c>
+      <c r="E77" s="2">
+        <v>46193.410856481481</v>
       </c>
       <c r="F77" s="1">
-        <v>46190</v>
+        <v>46193</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
-        <v>530025</v>
+        <v>530024</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>106</v>
@@ -3226,16 +3244,16 @@
         <v>0</v>
       </c>
       <c r="D78" s="1">
-        <v>269</v>
-      </c>
-      <c r="E78" s="1">
-        <v>46193.410856481481</v>
+        <v>279</v>
+      </c>
+      <c r="E78" s="2">
+        <v>46234.387870370374</v>
       </c>
       <c r="F78" s="1">
-        <v>46193</v>
+        <v>46234</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>31</v>
@@ -3243,25 +3261,25 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
-        <v>530024</v>
+        <v>530023</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C79" s="1">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="D79" s="1">
-        <v>279</v>
-      </c>
-      <c r="E79" s="1">
-        <v>46234.387870370374</v>
+        <v>329</v>
+      </c>
+      <c r="E79" s="2">
+        <v>46191.570451388892</v>
       </c>
       <c r="F79" s="1">
-        <v>46234</v>
+        <v>46191</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>31</v>
@@ -3269,25 +3287,25 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
-        <v>530023</v>
+        <v>530039</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C80" s="1">
-        <v>53</v>
+        <v>-353</v>
       </c>
       <c r="D80" s="1">
-        <v>329</v>
-      </c>
-      <c r="E80" s="1">
-        <v>46191.570451388892</v>
+        <v>290</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46237.145567129628</v>
       </c>
       <c r="F80" s="1">
-        <v>46191</v>
+        <v>46237</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>31</v>
@@ -3295,25 +3313,25 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
-        <v>530039</v>
+        <v>530021</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C81" s="1">
-        <v>-353</v>
+        <v>0</v>
       </c>
       <c r="D81" s="1">
-        <v>290</v>
-      </c>
-      <c r="E81" s="1">
+        <v>41.1</v>
+      </c>
+      <c r="E81" s="2">
         <v>46237.145567129628</v>
       </c>
       <c r="F81" s="1">
         <v>46237</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>31</v>
@@ -3321,25 +3339,25 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
-        <v>530021</v>
+        <v>530020</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C82" s="1">
-        <v>0</v>
+        <v>-282</v>
       </c>
       <c r="D82" s="1">
-        <v>41.1</v>
-      </c>
-      <c r="E82" s="1">
-        <v>46237.145567129628</v>
+        <v>23.1</v>
+      </c>
+      <c r="E82" s="2">
+        <v>46232.404004629629</v>
       </c>
       <c r="F82" s="1">
-        <v>46237</v>
+        <v>46232</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>31</v>
@@ -3347,25 +3365,25 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
-        <v>530020</v>
+        <v>530019</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>112</v>
       </c>
       <c r="C83" s="1">
-        <v>-282</v>
+        <v>0</v>
       </c>
       <c r="D83" s="1">
-        <v>23.1</v>
-      </c>
-      <c r="E83" s="1">
-        <v>46232.404004629629</v>
+        <v>203.88</v>
+      </c>
+      <c r="E83" s="2">
+        <v>46190.458101851851</v>
       </c>
       <c r="F83" s="1">
-        <v>46232</v>
+        <v>46190</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>31</v>
@@ -3373,7 +3391,7 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
-        <v>530019</v>
+        <v>530058</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>113</v>
@@ -3382,16 +3400,16 @@
         <v>0</v>
       </c>
       <c r="D84" s="1">
-        <v>203.88</v>
-      </c>
-      <c r="E84" s="1">
-        <v>46190.458101851851</v>
+        <v>145.35</v>
+      </c>
+      <c r="E84" s="2">
+        <v>46225.532627314817</v>
       </c>
       <c r="F84" s="1">
-        <v>46190</v>
+        <v>46225</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>31</v>
@@ -3399,7 +3417,7 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
-        <v>530058</v>
+        <v>530018</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>114</v>
@@ -3408,16 +3426,16 @@
         <v>0</v>
       </c>
       <c r="D85" s="1">
-        <v>145.35</v>
-      </c>
-      <c r="E85" s="1">
-        <v>46225.532627314817</v>
+        <v>218.95</v>
+      </c>
+      <c r="E85" s="2">
+        <v>46191.558136574073</v>
       </c>
       <c r="F85" s="1">
-        <v>46225</v>
+        <v>46191</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>31</v>
@@ -3425,7 +3443,7 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
-        <v>530032</v>
+        <v>530033</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>115</v>
@@ -3434,16 +3452,16 @@
         <v>0</v>
       </c>
       <c r="D86" s="1">
-        <v>-6.8</v>
-      </c>
-      <c r="E86" s="1">
-        <v>46205.407361111109</v>
+        <v>3</v>
+      </c>
+      <c r="E86" s="2">
+        <v>46234.597777777781</v>
       </c>
       <c r="F86" s="1">
-        <v>46205</v>
+        <v>46234</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>31</v>
@@ -3451,7 +3469,7 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
-        <v>530018</v>
+        <v>530059</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>116</v>
@@ -3460,16 +3478,16 @@
         <v>0</v>
       </c>
       <c r="D87" s="1">
-        <v>218.95</v>
-      </c>
-      <c r="E87" s="1">
-        <v>46191.558136574073</v>
+        <v>85.65</v>
+      </c>
+      <c r="E87" s="2">
+        <v>46237.360995370371</v>
       </c>
       <c r="F87" s="1">
-        <v>46191</v>
+        <v>46237</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>31</v>
@@ -3477,25 +3495,25 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
-        <v>530033</v>
+        <v>510002</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C88" s="1">
-        <v>0</v>
+        <v>-232</v>
       </c>
       <c r="D88" s="1">
-        <v>3</v>
-      </c>
-      <c r="E88" s="1">
-        <v>46234.597777777781</v>
+        <v>0.1</v>
+      </c>
+      <c r="E88" s="2">
+        <v>46237.524363425924</v>
       </c>
       <c r="F88" s="1">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>31</v>
@@ -3503,71 +3521,71 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
-        <v>530059</v>
+        <v>541506</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C89" s="1">
         <v>0</v>
       </c>
       <c r="D89" s="1">
-        <v>85.65</v>
-      </c>
-      <c r="E89" s="1">
-        <v>46237.360995370371</v>
+        <v>23</v>
+      </c>
+      <c r="E89" s="2">
+        <v>46234.616018518522</v>
       </c>
       <c r="F89" s="1">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
-        <v>510002</v>
+        <v>510302</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C90" s="1">
-        <v>-232</v>
+        <v>0</v>
       </c>
       <c r="D90" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="E90" s="1">
-        <v>46237.524363425924</v>
+        <v>0.85</v>
+      </c>
+      <c r="E90" s="2">
+        <v>46193.468148148146</v>
       </c>
       <c r="F90" s="1">
-        <v>46237</v>
+        <v>46193</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
-        <v>541506</v>
+        <v>141302</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>121</v>
       </c>
       <c r="C91" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D91" s="1">
-        <v>23</v>
-      </c>
-      <c r="E91" s="1">
-        <v>46234.616018518522</v>
+        <v>24</v>
+      </c>
+      <c r="E91" s="2">
+        <v>46234.621759259258</v>
       </c>
       <c r="F91" s="1">
         <v>46234</v>
@@ -3581,7 +3599,7 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
-        <v>510302</v>
+        <v>543042</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>122</v>
@@ -3590,42 +3608,42 @@
         <v>0</v>
       </c>
       <c r="D92" s="1">
-        <v>0.85</v>
-      </c>
-      <c r="E92" s="1">
-        <v>46193.468148148146</v>
+        <v>239</v>
+      </c>
+      <c r="E92" s="2">
+        <v>46234.612314814818</v>
       </c>
       <c r="F92" s="1">
-        <v>46193</v>
+        <v>46234</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
-        <v>141302</v>
+        <v>542041</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>123</v>
       </c>
       <c r="C93" s="1">
-        <v>16</v>
+        <v>-104</v>
       </c>
       <c r="D93" s="1">
-        <v>24</v>
-      </c>
-      <c r="E93" s="1">
-        <v>46234.621759259258</v>
+        <v>190</v>
+      </c>
+      <c r="E93" s="2">
+        <v>46225.538622685184</v>
       </c>
       <c r="F93" s="1">
-        <v>46234</v>
+        <v>46225</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>14</v>
@@ -3633,25 +3651,25 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
-        <v>543042</v>
+        <v>542035</v>
       </c>
       <c r="B94" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C94" s="1">
+        <v>-738</v>
+      </c>
+      <c r="D94" s="1">
+        <v>432</v>
+      </c>
+      <c r="E94" s="2">
+        <v>46234.623784722222</v>
+      </c>
+      <c r="F94" s="1">
+        <v>46234</v>
+      </c>
+      <c r="G94" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="C94" s="1">
-        <v>0</v>
-      </c>
-      <c r="D94" s="1">
-        <v>239</v>
-      </c>
-      <c r="E94" s="1">
-        <v>46234.612314814818</v>
-      </c>
-      <c r="F94" s="1">
-        <v>46234</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>14</v>
@@ -3659,25 +3677,25 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
-        <v>542041</v>
+        <v>542040</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C95" s="1">
-        <v>-104</v>
+        <v>0</v>
       </c>
       <c r="D95" s="1">
-        <v>190</v>
-      </c>
-      <c r="E95" s="1">
-        <v>46225.538622685184</v>
+        <v>291</v>
+      </c>
+      <c r="E95" s="2">
+        <v>46234.387870370374</v>
       </c>
       <c r="F95" s="1">
-        <v>46225</v>
+        <v>46234</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>126</v>
+        <v>78</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>14</v>
@@ -3685,33 +3703,33 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
-        <v>542035</v>
+        <v>530305</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>127</v>
       </c>
       <c r="C96" s="1">
-        <v>-738</v>
+        <v>0</v>
       </c>
       <c r="D96" s="1">
-        <v>432</v>
-      </c>
-      <c r="E96" s="1">
-        <v>46234.623784722222</v>
+        <v>11</v>
+      </c>
+      <c r="E96" s="2">
+        <v>46195.890023148146</v>
       </c>
       <c r="F96" s="1">
-        <v>46234</v>
+        <v>46195</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>126</v>
+        <v>78</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
-        <v>542040</v>
+        <v>530306</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>128</v>
@@ -3720,24 +3738,24 @@
         <v>0</v>
       </c>
       <c r="D97" s="1">
-        <v>291</v>
-      </c>
-      <c r="E97" s="1">
-        <v>46234.387870370374</v>
+        <v>234</v>
+      </c>
+      <c r="E97" s="2">
+        <v>46198.631712962961</v>
       </c>
       <c r="F97" s="1">
-        <v>46234</v>
+        <v>46198</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
-        <v>530305</v>
+        <v>540107</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>129</v>
@@ -3746,24 +3764,24 @@
         <v>0</v>
       </c>
       <c r="D98" s="1">
-        <v>11</v>
-      </c>
-      <c r="E98" s="1">
-        <v>46195.890023148146</v>
+        <v>168</v>
+      </c>
+      <c r="E98" s="2">
+        <v>46225.565937500003</v>
       </c>
       <c r="F98" s="1">
-        <v>46195</v>
+        <v>46225</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
-        <v>530306</v>
+        <v>534511</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>130</v>
@@ -3772,16 +3790,16 @@
         <v>0</v>
       </c>
       <c r="D99" s="1">
-        <v>234</v>
-      </c>
-      <c r="E99" s="1">
-        <v>46198.631712962961</v>
+        <v>27</v>
+      </c>
+      <c r="E99" s="2">
+        <v>46230.735081018516</v>
       </c>
       <c r="F99" s="1">
-        <v>46198</v>
+        <v>46230</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>31</v>
@@ -3789,123 +3807,123 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
-        <v>540107</v>
+        <v>650124</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C100" s="1">
         <v>0</v>
       </c>
       <c r="D100" s="1">
-        <v>168</v>
-      </c>
-      <c r="E100" s="1">
-        <v>46225.565937500003</v>
+        <v>12</v>
+      </c>
+      <c r="E100" s="2">
+        <v>46231.808171296296</v>
       </c>
       <c r="F100" s="1">
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
-        <v>534511</v>
+        <v>650101</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C101" s="1">
         <v>0</v>
       </c>
       <c r="D101" s="1">
-        <v>27</v>
-      </c>
-      <c r="E101" s="1">
-        <v>46230.735081018516</v>
+        <v>6</v>
+      </c>
+      <c r="E101" s="2">
+        <v>46204.679166666669</v>
       </c>
       <c r="F101" s="1">
-        <v>46230</v>
+        <v>46204</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>133</v>
+        <v>9</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
-        <v>650124</v>
+        <v>650131</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>134</v>
       </c>
       <c r="C102" s="1">
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="D102" s="1">
-        <v>12</v>
-      </c>
-      <c r="E102" s="1">
-        <v>46231.808171296296</v>
+        <v>8</v>
+      </c>
+      <c r="E102" s="2">
+        <v>46225.590104166666</v>
       </c>
       <c r="F102" s="1">
-        <v>46231</v>
+        <v>46225</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
-        <v>650101</v>
+        <v>650121</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>135</v>
       </c>
       <c r="C103" s="1">
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="D103" s="1">
-        <v>6</v>
-      </c>
-      <c r="E103" s="1">
-        <v>46204.679166666669</v>
+        <v>7</v>
+      </c>
+      <c r="E103" s="2">
+        <v>46231.811585648145</v>
       </c>
       <c r="F103" s="1">
-        <v>46204</v>
+        <v>46231</v>
       </c>
       <c r="G103" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
-        <v>650131</v>
+        <v>550103</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>136</v>
       </c>
       <c r="C104" s="1">
-        <v>-34</v>
+        <v>-22</v>
       </c>
       <c r="D104" s="1">
-        <v>8</v>
-      </c>
-      <c r="E104" s="1">
-        <v>46225.590104166666</v>
+        <v>56</v>
+      </c>
+      <c r="E104" s="2">
+        <v>46225.589120370372</v>
       </c>
       <c r="F104" s="1">
         <v>46225</v>
@@ -3914,23 +3932,23 @@
         <v>9</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
-        <v>650121</v>
+        <v>550305</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>137</v>
       </c>
       <c r="C105" s="1">
-        <v>-22</v>
+        <v>-21</v>
       </c>
       <c r="D105" s="1">
-        <v>7</v>
-      </c>
-      <c r="E105" s="1">
+        <v>123</v>
+      </c>
+      <c r="E105" s="2">
         <v>46231.811585648145</v>
       </c>
       <c r="F105" s="1">
@@ -3940,23 +3958,23 @@
         <v>9</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
-        <v>550103</v>
+        <v>544100</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>138</v>
       </c>
       <c r="C106" s="1">
-        <v>-22</v>
+        <v>-20</v>
       </c>
       <c r="D106" s="1">
-        <v>56</v>
-      </c>
-      <c r="E106" s="1">
+        <v>90</v>
+      </c>
+      <c r="E106" s="2">
         <v>46225.589120370372</v>
       </c>
       <c r="F106" s="1">
@@ -3966,90 +3984,90 @@
         <v>9</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
-        <v>550305</v>
+        <v>650301</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>139</v>
       </c>
       <c r="C107" s="1">
-        <v>-21</v>
+        <v>-12</v>
       </c>
       <c r="D107" s="1">
-        <v>123</v>
-      </c>
-      <c r="E107" s="1">
-        <v>46231.811585648145</v>
+        <v>29</v>
+      </c>
+      <c r="E107" s="2">
+        <v>46203.745405092595</v>
       </c>
       <c r="F107" s="1">
-        <v>46231</v>
+        <v>46203</v>
       </c>
       <c r="G107" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
-        <v>544100</v>
+        <v>650112</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>140</v>
       </c>
       <c r="C108" s="1">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="D108" s="1">
-        <v>90</v>
-      </c>
-      <c r="E108" s="1">
-        <v>46225.589120370372</v>
+        <v>5</v>
+      </c>
+      <c r="E108" s="2">
+        <v>46203.745405092595</v>
       </c>
       <c r="F108" s="1">
-        <v>46225</v>
+        <v>46203</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
-        <v>650301</v>
+        <v>650102</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>141</v>
       </c>
       <c r="C109" s="1">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="D109" s="1">
-        <v>29</v>
-      </c>
-      <c r="E109" s="1">
+        <v>7</v>
+      </c>
+      <c r="E109" s="2">
         <v>46203.745405092595</v>
       </c>
       <c r="F109" s="1">
         <v>46203</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
-        <v>650112</v>
+        <v>650132</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>142</v>
@@ -4058,24 +4076,24 @@
         <v>0</v>
       </c>
       <c r="D110" s="1">
-        <v>5</v>
-      </c>
-      <c r="E110" s="1">
+        <v>13</v>
+      </c>
+      <c r="E110" s="2">
         <v>46203.745405092595</v>
       </c>
       <c r="F110" s="1">
         <v>46203</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
-        <v>650102</v>
+        <v>650122</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>143</v>
@@ -4084,24 +4102,24 @@
         <v>0</v>
       </c>
       <c r="D111" s="1">
-        <v>7</v>
-      </c>
-      <c r="E111" s="1">
+        <v>14</v>
+      </c>
+      <c r="E111" s="2">
         <v>46203.745405092595</v>
       </c>
       <c r="F111" s="1">
         <v>46203</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
-        <v>650132</v>
+        <v>650256</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>144</v>
@@ -4110,24 +4128,24 @@
         <v>0</v>
       </c>
       <c r="D112" s="1">
-        <v>13</v>
-      </c>
-      <c r="E112" s="1">
-        <v>46203.745405092595</v>
+        <v>73</v>
+      </c>
+      <c r="E112" s="2">
+        <v>46234.616550925923</v>
       </c>
       <c r="F112" s="1">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
-        <v>650122</v>
+        <v>650257</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>145</v>
@@ -4136,24 +4154,24 @@
         <v>0</v>
       </c>
       <c r="D113" s="1">
-        <v>14</v>
-      </c>
-      <c r="E113" s="1">
-        <v>46203.745405092595</v>
+        <v>13</v>
+      </c>
+      <c r="E113" s="2">
+        <v>46234.616550925923</v>
       </c>
       <c r="F113" s="1">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
-        <v>650256</v>
+        <v>650303</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>146</v>
@@ -4162,50 +4180,50 @@
         <v>0</v>
       </c>
       <c r="D114" s="1">
-        <v>73</v>
-      </c>
-      <c r="E114" s="1">
-        <v>46234.616550925923</v>
+        <v>53</v>
+      </c>
+      <c r="E114" s="2">
+        <v>46234.616018518522</v>
       </c>
       <c r="F114" s="1">
         <v>46234</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
-        <v>650257</v>
+        <v>650113</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>147</v>
       </c>
       <c r="C115" s="1">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="D115" s="1">
-        <v>13</v>
-      </c>
-      <c r="E115" s="1">
-        <v>46234.616550925923</v>
+        <v>15</v>
+      </c>
+      <c r="E115" s="2">
+        <v>46225.538622685184</v>
       </c>
       <c r="F115" s="1">
-        <v>46234</v>
+        <v>46225</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
-        <v>650303</v>
+        <v>650103</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>148</v>
@@ -4214,50 +4232,50 @@
         <v>0</v>
       </c>
       <c r="D116" s="1">
-        <v>53</v>
-      </c>
-      <c r="E116" s="1">
-        <v>46234.616018518522</v>
+        <v>21</v>
+      </c>
+      <c r="E116" s="2">
+        <v>46234.593993055554</v>
       </c>
       <c r="F116" s="1">
         <v>46234</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
-        <v>650113</v>
+        <v>650133</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>149</v>
       </c>
       <c r="C117" s="1">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="D117" s="1">
-        <v>15</v>
-      </c>
-      <c r="E117" s="1">
-        <v>46225.538622685184</v>
+        <v>20</v>
+      </c>
+      <c r="E117" s="2">
+        <v>46231.805069444446</v>
       </c>
       <c r="F117" s="1">
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
-        <v>650103</v>
+        <v>650123</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>150</v>
@@ -4266,102 +4284,102 @@
         <v>0</v>
       </c>
       <c r="D118" s="1">
-        <v>21</v>
-      </c>
-      <c r="E118" s="1">
-        <v>46234.593993055554</v>
+        <v>16</v>
+      </c>
+      <c r="E118" s="2">
+        <v>46234.621759259258</v>
       </c>
       <c r="F118" s="1">
         <v>46234</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>28</v>
+        <v>151</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
-        <v>650133</v>
+        <v>550108</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C119" s="1">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="D119" s="1">
-        <v>20</v>
-      </c>
-      <c r="E119" s="1">
-        <v>46231.805069444446</v>
+        <v>57</v>
+      </c>
+      <c r="E119" s="2">
+        <v>46205.430636574078</v>
       </c>
       <c r="F119" s="1">
-        <v>46231</v>
+        <v>46205</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>28</v>
+        <v>118</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
-        <v>650123</v>
+        <v>550303</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C120" s="1">
         <v>0</v>
       </c>
       <c r="D120" s="1">
-        <v>16</v>
-      </c>
-      <c r="E120" s="1">
-        <v>46234.621759259258</v>
+        <v>54</v>
+      </c>
+      <c r="E120" s="2">
+        <v>46205.430636574078</v>
       </c>
       <c r="F120" s="1">
-        <v>46234</v>
+        <v>46205</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>153</v>
+        <v>28</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
-        <v>550108</v>
+        <v>550302</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>154</v>
       </c>
       <c r="C121" s="1">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="D121" s="1">
-        <v>57</v>
-      </c>
-      <c r="E121" s="1">
-        <v>46205.430636574078</v>
+        <v>109</v>
+      </c>
+      <c r="E121" s="2">
+        <v>46234.612314814818</v>
       </c>
       <c r="F121" s="1">
-        <v>46205</v>
+        <v>46234</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
-        <v>550303</v>
+        <v>550102</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>155</v>
@@ -4370,24 +4388,24 @@
         <v>0</v>
       </c>
       <c r="D122" s="1">
-        <v>54</v>
-      </c>
-      <c r="E122" s="1">
-        <v>46205.430636574078</v>
+        <v>108</v>
+      </c>
+      <c r="E122" s="2">
+        <v>46225.465543981481</v>
       </c>
       <c r="F122" s="1">
-        <v>46205</v>
+        <v>46225</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
-        <v>550302</v>
+        <v>650114</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>156</v>
@@ -4396,24 +4414,24 @@
         <v>0</v>
       </c>
       <c r="D123" s="1">
-        <v>109</v>
-      </c>
-      <c r="E123" s="1">
-        <v>46234.612314814818</v>
+        <v>15</v>
+      </c>
+      <c r="E123" s="2">
+        <v>46234.604432870372</v>
       </c>
       <c r="F123" s="1">
         <v>46234</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>28</v>
+        <v>102</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
-        <v>550102</v>
+        <v>650104</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>157</v>
@@ -4422,24 +4440,24 @@
         <v>0</v>
       </c>
       <c r="D124" s="1">
-        <v>108</v>
-      </c>
-      <c r="E124" s="1">
-        <v>46225.465543981481</v>
+        <v>8</v>
+      </c>
+      <c r="E124" s="2">
+        <v>46234.604432870372</v>
       </c>
       <c r="F124" s="1">
-        <v>46225</v>
+        <v>46234</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
-        <v>650114</v>
+        <v>650134</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>158</v>
@@ -4448,24 +4466,24 @@
         <v>0</v>
       </c>
       <c r="D125" s="1">
-        <v>15</v>
-      </c>
-      <c r="E125" s="1">
-        <v>46234.604432870372</v>
+        <v>6</v>
+      </c>
+      <c r="E125" s="2">
+        <v>46234.387870370374</v>
       </c>
       <c r="F125" s="1">
         <v>46234</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
-        <v>650104</v>
+        <v>560103</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>159</v>
@@ -4474,9 +4492,9 @@
         <v>0</v>
       </c>
       <c r="D126" s="1">
-        <v>8</v>
-      </c>
-      <c r="E126" s="1">
+        <v>15</v>
+      </c>
+      <c r="E126" s="2">
         <v>46234.604432870372</v>
       </c>
       <c r="F126" s="1">
@@ -4486,12 +4504,12 @@
         <v>23</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
-        <v>650134</v>
+        <v>560105</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>160</v>
@@ -4500,24 +4518,24 @@
         <v>0</v>
       </c>
       <c r="D127" s="1">
-        <v>6</v>
-      </c>
-      <c r="E127" s="1">
-        <v>46234.387870370374</v>
+        <v>54</v>
+      </c>
+      <c r="E127" s="2">
+        <v>46230.73369212963</v>
       </c>
       <c r="F127" s="1">
-        <v>46234</v>
+        <v>46230</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
-        <v>560103</v>
+        <v>560101</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>161</v>
@@ -4526,24 +4544,24 @@
         <v>0</v>
       </c>
       <c r="D128" s="1">
-        <v>15</v>
-      </c>
-      <c r="E128" s="1">
-        <v>46234.604432870372</v>
+        <v>39</v>
+      </c>
+      <c r="E128" s="2">
+        <v>46234.593993055554</v>
       </c>
       <c r="F128" s="1">
         <v>46234</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
-        <v>560105</v>
+        <v>640000</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>162</v>
@@ -4552,50 +4570,50 @@
         <v>0</v>
       </c>
       <c r="D129" s="1">
-        <v>54</v>
-      </c>
-      <c r="E129" s="1">
-        <v>46230.73369212963</v>
+        <v>38</v>
+      </c>
+      <c r="E129" s="2">
+        <v>46234.612314814818</v>
       </c>
       <c r="F129" s="1">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>133</v>
+        <v>28</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
-        <v>560101</v>
+        <v>640002</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>163</v>
       </c>
       <c r="C130" s="1">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="D130" s="1">
-        <v>39</v>
-      </c>
-      <c r="E130" s="1">
-        <v>46234.593993055554</v>
+        <v>11</v>
+      </c>
+      <c r="E130" s="2">
+        <v>46234.597777777781</v>
       </c>
       <c r="F130" s="1">
         <v>46234</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>28</v>
+        <v>102</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
-        <v>640000</v>
+        <v>641004</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>164</v>
@@ -4604,180 +4622,180 @@
         <v>0</v>
       </c>
       <c r="D131" s="1">
-        <v>38</v>
-      </c>
-      <c r="E131" s="1">
-        <v>46234.612314814818</v>
+        <v>9</v>
+      </c>
+      <c r="E131" s="2">
+        <v>46234.604432870372</v>
       </c>
       <c r="F131" s="1">
         <v>46234</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
-        <v>640002</v>
+        <v>640007</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>165</v>
       </c>
       <c r="C132" s="1">
-        <v>-12</v>
+        <v>-25</v>
       </c>
       <c r="D132" s="1">
-        <v>11</v>
-      </c>
-      <c r="E132" s="1">
-        <v>46234.597777777781</v>
+        <v>49</v>
+      </c>
+      <c r="E132" s="2">
+        <v>46212.278252314813</v>
       </c>
       <c r="F132" s="1">
-        <v>46234</v>
+        <v>46212</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
-        <v>641004</v>
+        <v>550420</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>166</v>
       </c>
       <c r="C133" s="1">
-        <v>0</v>
+        <v>-47</v>
       </c>
       <c r="D133" s="1">
-        <v>9</v>
-      </c>
-      <c r="E133" s="1">
-        <v>46234.604432870372</v>
+        <v>108</v>
+      </c>
+      <c r="E133" s="2">
+        <v>46234.623784722222</v>
       </c>
       <c r="F133" s="1">
         <v>46234</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
-        <v>640007</v>
+        <v>650200</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>167</v>
       </c>
       <c r="C134" s="1">
-        <v>-25</v>
+        <v>-10</v>
       </c>
       <c r="D134" s="1">
-        <v>49</v>
-      </c>
-      <c r="E134" s="1">
-        <v>46212.278252314813</v>
+        <v>335</v>
+      </c>
+      <c r="E134" s="2">
+        <v>46234.597777777781</v>
       </c>
       <c r="F134" s="1">
-        <v>46212</v>
+        <v>46234</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
-        <v>550420</v>
+        <v>541571</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>168</v>
       </c>
       <c r="C135" s="1">
-        <v>-47</v>
+        <v>-6</v>
       </c>
       <c r="D135" s="1">
-        <v>108</v>
-      </c>
-      <c r="E135" s="1">
-        <v>46234.623784722222</v>
+        <v>301</v>
+      </c>
+      <c r="E135" s="2">
+        <v>46231.811585648145</v>
       </c>
       <c r="F135" s="1">
-        <v>46234</v>
+        <v>46231</v>
       </c>
       <c r="G135" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H135" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="H135" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
-        <v>650200</v>
+        <v>540102</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>169</v>
       </c>
       <c r="C136" s="1">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="D136" s="1">
-        <v>335</v>
-      </c>
-      <c r="E136" s="1">
-        <v>46234.597777777781</v>
+        <v>85</v>
+      </c>
+      <c r="E136" s="2">
+        <v>46234.612314814818</v>
       </c>
       <c r="F136" s="1">
         <v>46234</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
-        <v>541571</v>
+        <v>590104</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>170</v>
       </c>
       <c r="C137" s="1">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="D137" s="1">
-        <v>301</v>
-      </c>
-      <c r="E137" s="1">
-        <v>46231.811585648145</v>
+        <v>1</v>
+      </c>
+      <c r="E137" s="2">
+        <v>46225.46365740741</v>
       </c>
       <c r="F137" s="1">
-        <v>46231</v>
+        <v>46225</v>
       </c>
       <c r="G137" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H137" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="H137" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
-        <v>540102</v>
+        <v>590244</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>171</v>
@@ -4786,50 +4804,50 @@
         <v>0</v>
       </c>
       <c r="D138" s="1">
-        <v>85</v>
-      </c>
-      <c r="E138" s="1">
-        <v>46234.612314814818</v>
+        <v>206</v>
+      </c>
+      <c r="E138" s="2">
+        <v>46231.811585648145</v>
       </c>
       <c r="F138" s="1">
-        <v>46234</v>
+        <v>46231</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
-        <v>590104</v>
+        <v>590211</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>172</v>
       </c>
       <c r="C139" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D139" s="1">
-        <v>1</v>
-      </c>
-      <c r="E139" s="1">
-        <v>46225.46365740741</v>
+        <v>27</v>
+      </c>
+      <c r="E139" s="2">
+        <v>46234.602418981478</v>
       </c>
       <c r="F139" s="1">
-        <v>46225</v>
+        <v>46234</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
-        <v>590244</v>
+        <v>590210</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>173</v>
@@ -4838,35 +4856,35 @@
         <v>0</v>
       </c>
       <c r="D140" s="1">
-        <v>206</v>
-      </c>
-      <c r="E140" s="1">
-        <v>46231.811585648145</v>
+        <v>173</v>
+      </c>
+      <c r="E140" s="2">
+        <v>46234.602418981478</v>
       </c>
       <c r="F140" s="1">
-        <v>46231</v>
+        <v>46234</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
-        <v>590211</v>
+        <v>590209</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>174</v>
       </c>
       <c r="C141" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D141" s="1">
-        <v>27</v>
-      </c>
-      <c r="E141" s="1">
+        <v>386</v>
+      </c>
+      <c r="E141" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F141" s="1">
@@ -4876,38 +4894,38 @@
         <v>35</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
-        <v>590210</v>
+        <v>590208</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>175</v>
       </c>
       <c r="C142" s="1">
-        <v>0</v>
+        <v>-52</v>
       </c>
       <c r="D142" s="1">
-        <v>173</v>
-      </c>
-      <c r="E142" s="1">
-        <v>46234.602418981478</v>
+        <v>668</v>
+      </c>
+      <c r="E142" s="2">
+        <v>46234.616018518522</v>
       </c>
       <c r="F142" s="1">
         <v>46234</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
-        <v>590209</v>
+        <v>550911</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>176</v>
@@ -4916,50 +4934,50 @@
         <v>0</v>
       </c>
       <c r="D143" s="1">
-        <v>386</v>
-      </c>
-      <c r="E143" s="1">
-        <v>46234.602418981478</v>
+        <v>128</v>
+      </c>
+      <c r="E143" s="2">
+        <v>46218.585393518515</v>
       </c>
       <c r="F143" s="1">
-        <v>46234</v>
+        <v>46218</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
-        <v>590208</v>
+        <v>550912</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>177</v>
       </c>
       <c r="C144" s="1">
-        <v>-52</v>
+        <v>0</v>
       </c>
       <c r="D144" s="1">
-        <v>668</v>
-      </c>
-      <c r="E144" s="1">
-        <v>46234.616018518522</v>
+        <v>134</v>
+      </c>
+      <c r="E144" s="2">
+        <v>46231.807766203703</v>
       </c>
       <c r="F144" s="1">
-        <v>46234</v>
+        <v>46231</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
-        <v>590228</v>
+        <v>550917</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>178</v>
@@ -4968,24 +4986,24 @@
         <v>0</v>
       </c>
       <c r="D145" s="1">
-        <v>-15</v>
-      </c>
-      <c r="E145" s="1">
-        <v>46234.616018518522</v>
+        <v>139</v>
+      </c>
+      <c r="E145" s="2">
+        <v>46219.354791666665</v>
       </c>
       <c r="F145" s="1">
-        <v>46234</v>
+        <v>46219</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>35</v>
+        <v>118</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
-        <v>550911</v>
+        <v>550915</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>179</v>
@@ -4994,24 +5012,24 @@
         <v>0</v>
       </c>
       <c r="D146" s="1">
-        <v>128</v>
-      </c>
-      <c r="E146" s="1">
-        <v>46218.585393518515</v>
+        <v>108</v>
+      </c>
+      <c r="E146" s="2">
+        <v>46236.327384259261</v>
       </c>
       <c r="F146" s="1">
-        <v>46218</v>
+        <v>46236</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
-        <v>550912</v>
+        <v>651250</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>180</v>
@@ -5020,24 +5038,24 @@
         <v>0</v>
       </c>
       <c r="D147" s="1">
-        <v>134</v>
-      </c>
-      <c r="E147" s="1">
-        <v>46231.807766203703</v>
+        <v>6</v>
+      </c>
+      <c r="E147" s="2">
+        <v>46231.805069444446</v>
       </c>
       <c r="F147" s="1">
         <v>46231</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
-        <v>550917</v>
+        <v>651251</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>181</v>
@@ -5046,50 +5064,50 @@
         <v>0</v>
       </c>
       <c r="D148" s="1">
-        <v>139</v>
-      </c>
-      <c r="E148" s="1">
-        <v>46219.354791666665</v>
+        <v>7</v>
+      </c>
+      <c r="E148" s="2">
+        <v>46224.486076388886</v>
       </c>
       <c r="F148" s="1">
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>120</v>
+        <v>47</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
-        <v>550915</v>
+        <v>541510</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>182</v>
       </c>
       <c r="C149" s="1">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="D149" s="1">
-        <v>108</v>
-      </c>
-      <c r="E149" s="1">
-        <v>46236.327384259261</v>
+        <v>155</v>
+      </c>
+      <c r="E149" s="2">
+        <v>46234.616018518522</v>
       </c>
       <c r="F149" s="1">
-        <v>46236</v>
+        <v>46234</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
-        <v>651250</v>
+        <v>541515</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>183</v>
@@ -5098,68 +5116,68 @@
         <v>0</v>
       </c>
       <c r="D150" s="1">
-        <v>6</v>
-      </c>
-      <c r="E150" s="1">
-        <v>46231.805069444446</v>
+        <v>71</v>
+      </c>
+      <c r="E150" s="2">
+        <v>46234.616886574076</v>
       </c>
       <c r="F150" s="1">
-        <v>46231</v>
+        <v>46234</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
-        <v>651251</v>
+        <v>541516</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>184</v>
       </c>
       <c r="C151" s="1">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D151" s="1">
-        <v>7</v>
-      </c>
-      <c r="E151" s="1">
-        <v>46224.486076388886</v>
+        <v>66</v>
+      </c>
+      <c r="E151" s="2">
+        <v>46230.73369212963</v>
       </c>
       <c r="F151" s="1">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
-        <v>541510</v>
+        <v>541504</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>185</v>
       </c>
       <c r="C152" s="1">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="D152" s="1">
-        <v>155</v>
-      </c>
-      <c r="E152" s="1">
-        <v>46234.616018518522</v>
+        <v>218</v>
+      </c>
+      <c r="E152" s="2">
+        <v>46230.73369212963</v>
       </c>
       <c r="F152" s="1">
-        <v>46234</v>
+        <v>46230</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="H152" s="1" t="s">
         <v>14</v>
@@ -5167,7 +5185,7 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
-        <v>541515</v>
+        <v>541605</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>186</v>
@@ -5176,16 +5194,16 @@
         <v>0</v>
       </c>
       <c r="D153" s="1">
-        <v>71</v>
-      </c>
-      <c r="E153" s="1">
-        <v>46234.616886574076</v>
+        <v>164</v>
+      </c>
+      <c r="E153" s="2">
+        <v>46230.735081018516</v>
       </c>
       <c r="F153" s="1">
-        <v>46234</v>
+        <v>46230</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>28</v>
+        <v>131</v>
       </c>
       <c r="H153" s="1" t="s">
         <v>14</v>
@@ -5193,33 +5211,33 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
-        <v>541516</v>
+        <v>530321</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>187</v>
       </c>
       <c r="C154" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D154" s="1">
-        <v>66</v>
-      </c>
-      <c r="E154" s="1">
-        <v>46230.73369212963</v>
+        <v>34</v>
+      </c>
+      <c r="E154" s="2">
+        <v>46234.602418981478</v>
       </c>
       <c r="F154" s="1">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
-        <v>541504</v>
+        <v>660003</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>188</v>
@@ -5228,24 +5246,24 @@
         <v>0</v>
       </c>
       <c r="D155" s="1">
-        <v>218</v>
-      </c>
-      <c r="E155" s="1">
-        <v>46230.73369212963</v>
+        <v>27</v>
+      </c>
+      <c r="E155" s="2">
+        <v>46234.602418981478</v>
       </c>
       <c r="F155" s="1">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
-        <v>541605</v>
+        <v>550503</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>189</v>
@@ -5254,24 +5272,24 @@
         <v>0</v>
       </c>
       <c r="D156" s="1">
-        <v>164</v>
-      </c>
-      <c r="E156" s="1">
-        <v>46230.735081018516</v>
+        <v>9</v>
+      </c>
+      <c r="E156" s="2">
+        <v>46234.602418981478</v>
       </c>
       <c r="F156" s="1">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
-        <v>530321</v>
+        <v>550501</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>190</v>
@@ -5280,24 +5298,24 @@
         <v>0</v>
       </c>
       <c r="D157" s="1">
-        <v>34</v>
-      </c>
-      <c r="E157" s="1">
+        <v>1</v>
+      </c>
+      <c r="E157" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F157" s="1">
         <v>46234</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
-        <v>660003</v>
+        <v>544109</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>191</v>
@@ -5306,24 +5324,24 @@
         <v>0</v>
       </c>
       <c r="D158" s="1">
-        <v>27</v>
-      </c>
-      <c r="E158" s="1">
+        <v>14</v>
+      </c>
+      <c r="E158" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F158" s="1">
         <v>46234</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
-        <v>550503</v>
+        <v>560510</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>192</v>
@@ -5332,24 +5350,24 @@
         <v>0</v>
       </c>
       <c r="D159" s="1">
-        <v>9</v>
-      </c>
-      <c r="E159" s="1">
+        <v>33</v>
+      </c>
+      <c r="E159" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F159" s="1">
         <v>46234</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
-        <v>550501</v>
+        <v>560503</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>193</v>
@@ -5358,24 +5376,24 @@
         <v>0</v>
       </c>
       <c r="D160" s="1">
-        <v>1</v>
-      </c>
-      <c r="E160" s="1">
+        <v>14</v>
+      </c>
+      <c r="E160" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F160" s="1">
         <v>46234</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
-        <v>544109</v>
+        <v>541612</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>194</v>
@@ -5384,16 +5402,16 @@
         <v>0</v>
       </c>
       <c r="D161" s="1">
-        <v>14</v>
-      </c>
-      <c r="E161" s="1">
+        <v>9</v>
+      </c>
+      <c r="E161" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F161" s="1">
         <v>46234</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H161" s="1" t="s">
         <v>14</v>
@@ -5401,7 +5419,7 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
-        <v>560510</v>
+        <v>520303</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>195</v>
@@ -5410,24 +5428,24 @@
         <v>0</v>
       </c>
       <c r="D162" s="1">
-        <v>33</v>
-      </c>
-      <c r="E162" s="1">
+        <v>159</v>
+      </c>
+      <c r="E162" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F162" s="1">
         <v>46234</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>84</v>
+        <v>31</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
-        <v>560503</v>
+        <v>540316</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>196</v>
@@ -5436,24 +5454,24 @@
         <v>0</v>
       </c>
       <c r="D163" s="1">
-        <v>14</v>
-      </c>
-      <c r="E163" s="1">
+        <v>386</v>
+      </c>
+      <c r="E163" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F163" s="1">
         <v>46234</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
-        <v>541612</v>
+        <v>540024</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>197</v>
@@ -5462,16 +5480,16 @@
         <v>0</v>
       </c>
       <c r="D164" s="1">
-        <v>9</v>
-      </c>
-      <c r="E164" s="1">
+        <v>82</v>
+      </c>
+      <c r="E164" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F164" s="1">
         <v>46234</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H164" s="1" t="s">
         <v>14</v>
@@ -5479,7 +5497,7 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
-        <v>520303</v>
+        <v>540098</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>198</v>
@@ -5488,24 +5506,24 @@
         <v>0</v>
       </c>
       <c r="D165" s="1">
-        <v>159</v>
-      </c>
-      <c r="E165" s="1">
+        <v>37</v>
+      </c>
+      <c r="E165" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F165" s="1">
         <v>46234</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
-        <v>540316</v>
+        <v>540305</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>199</v>
@@ -5514,16 +5532,16 @@
         <v>0</v>
       </c>
       <c r="D166" s="1">
-        <v>386</v>
-      </c>
-      <c r="E166" s="1">
+        <v>185</v>
+      </c>
+      <c r="E166" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F166" s="1">
         <v>46234</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H166" s="1" t="s">
         <v>14</v>
@@ -5531,7 +5549,7 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
-        <v>540024</v>
+        <v>540090</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>200</v>
@@ -5540,16 +5558,16 @@
         <v>0</v>
       </c>
       <c r="D167" s="1">
-        <v>82</v>
-      </c>
-      <c r="E167" s="1">
+        <v>74</v>
+      </c>
+      <c r="E167" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F167" s="1">
         <v>46234</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H167" s="1" t="s">
         <v>14</v>
@@ -5557,7 +5575,7 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
-        <v>540098</v>
+        <v>540111</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>201</v>
@@ -5566,16 +5584,16 @@
         <v>0</v>
       </c>
       <c r="D168" s="1">
-        <v>37</v>
-      </c>
-      <c r="E168" s="1">
+        <v>1008</v>
+      </c>
+      <c r="E168" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F168" s="1">
         <v>46234</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H168" s="1" t="s">
         <v>14</v>
@@ -5583,7 +5601,7 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
-        <v>540305</v>
+        <v>540304</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>202</v>
@@ -5592,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="D169" s="1">
-        <v>185</v>
-      </c>
-      <c r="E169" s="1">
+        <v>200</v>
+      </c>
+      <c r="E169" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F169" s="1">
         <v>46234</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H169" s="1" t="s">
         <v>14</v>
@@ -5609,7 +5627,7 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
-        <v>540090</v>
+        <v>541517</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>203</v>
@@ -5618,16 +5636,16 @@
         <v>0</v>
       </c>
       <c r="D170" s="1">
-        <v>74</v>
-      </c>
-      <c r="E170" s="1">
+        <v>1</v>
+      </c>
+      <c r="E170" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F170" s="1">
         <v>46234</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H170" s="1" t="s">
         <v>14</v>
@@ -5635,7 +5653,7 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
-        <v>540111</v>
+        <v>541586</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>204</v>
@@ -5644,16 +5662,16 @@
         <v>0</v>
       </c>
       <c r="D171" s="1">
-        <v>1008</v>
-      </c>
-      <c r="E171" s="1">
+        <v>31</v>
+      </c>
+      <c r="E171" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F171" s="1">
         <v>46234</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H171" s="1" t="s">
         <v>14</v>
@@ -5661,7 +5679,7 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
-        <v>540304</v>
+        <v>541559</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>205</v>
@@ -5670,16 +5688,16 @@
         <v>0</v>
       </c>
       <c r="D172" s="1">
-        <v>200</v>
-      </c>
-      <c r="E172" s="1">
+        <v>37</v>
+      </c>
+      <c r="E172" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F172" s="1">
         <v>46234</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H172" s="1" t="s">
         <v>14</v>
@@ -5687,7 +5705,7 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
-        <v>541517</v>
+        <v>540108</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>206</v>
@@ -5696,16 +5714,16 @@
         <v>0</v>
       </c>
       <c r="D173" s="1">
-        <v>1</v>
-      </c>
-      <c r="E173" s="1">
+        <v>252</v>
+      </c>
+      <c r="E173" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F173" s="1">
         <v>46234</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H173" s="1" t="s">
         <v>14</v>
@@ -5713,7 +5731,7 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
-        <v>541586</v>
+        <v>540114</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>207</v>
@@ -5722,16 +5740,16 @@
         <v>0</v>
       </c>
       <c r="D174" s="1">
-        <v>31</v>
-      </c>
-      <c r="E174" s="1">
+        <v>27</v>
+      </c>
+      <c r="E174" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F174" s="1">
         <v>46234</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H174" s="1" t="s">
         <v>14</v>
@@ -5739,7 +5757,7 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
-        <v>541559</v>
+        <v>540094</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>208</v>
@@ -5748,16 +5766,16 @@
         <v>0</v>
       </c>
       <c r="D175" s="1">
-        <v>37</v>
-      </c>
-      <c r="E175" s="1">
+        <v>201</v>
+      </c>
+      <c r="E175" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F175" s="1">
         <v>46234</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H175" s="1" t="s">
         <v>14</v>
@@ -5765,7 +5783,7 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
-        <v>540108</v>
+        <v>540117</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>209</v>
@@ -5774,16 +5792,16 @@
         <v>0</v>
       </c>
       <c r="D176" s="1">
-        <v>252</v>
-      </c>
-      <c r="E176" s="1">
+        <v>70</v>
+      </c>
+      <c r="E176" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F176" s="1">
         <v>46234</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H176" s="1" t="s">
         <v>14</v>
@@ -5791,7 +5809,7 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
-        <v>540114</v>
+        <v>540096</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>210</v>
@@ -5800,16 +5818,16 @@
         <v>0</v>
       </c>
       <c r="D177" s="1">
-        <v>27</v>
-      </c>
-      <c r="E177" s="1">
+        <v>135</v>
+      </c>
+      <c r="E177" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F177" s="1">
         <v>46234</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H177" s="1" t="s">
         <v>14</v>
@@ -5817,7 +5835,7 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
-        <v>540094</v>
+        <v>540106</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>211</v>
@@ -5826,16 +5844,16 @@
         <v>0</v>
       </c>
       <c r="D178" s="1">
-        <v>201</v>
-      </c>
-      <c r="E178" s="1">
+        <v>643</v>
+      </c>
+      <c r="E178" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F178" s="1">
         <v>46234</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H178" s="1" t="s">
         <v>14</v>
@@ -5843,7 +5861,7 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
-        <v>540117</v>
+        <v>540092</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>212</v>
@@ -5852,16 +5870,16 @@
         <v>0</v>
       </c>
       <c r="D179" s="1">
-        <v>70</v>
-      </c>
-      <c r="E179" s="1">
+        <v>91</v>
+      </c>
+      <c r="E179" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F179" s="1">
         <v>46234</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H179" s="1" t="s">
         <v>14</v>
@@ -5869,7 +5887,7 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
-        <v>540096</v>
+        <v>540104</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>213</v>
@@ -5878,16 +5896,16 @@
         <v>0</v>
       </c>
       <c r="D180" s="1">
-        <v>135</v>
-      </c>
-      <c r="E180" s="1">
+        <v>88</v>
+      </c>
+      <c r="E180" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F180" s="1">
         <v>46234</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H180" s="1" t="s">
         <v>14</v>
@@ -5895,7 +5913,7 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
-        <v>540106</v>
+        <v>540036</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>214</v>
@@ -5904,16 +5922,16 @@
         <v>0</v>
       </c>
       <c r="D181" s="1">
-        <v>643</v>
-      </c>
-      <c r="E181" s="1">
+        <v>218</v>
+      </c>
+      <c r="E181" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F181" s="1">
         <v>46234</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H181" s="1" t="s">
         <v>14</v>
@@ -5921,7 +5939,7 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
-        <v>540092</v>
+        <v>540014</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>215</v>
@@ -5930,16 +5948,16 @@
         <v>0</v>
       </c>
       <c r="D182" s="1">
-        <v>91</v>
-      </c>
-      <c r="E182" s="1">
+        <v>56</v>
+      </c>
+      <c r="E182" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F182" s="1">
         <v>46234</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H182" s="1" t="s">
         <v>14</v>
@@ -5947,7 +5965,7 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
-        <v>540104</v>
+        <v>540035</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>216</v>
@@ -5956,16 +5974,16 @@
         <v>0</v>
       </c>
       <c r="D183" s="1">
-        <v>88</v>
-      </c>
-      <c r="E183" s="1">
+        <v>250</v>
+      </c>
+      <c r="E183" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F183" s="1">
         <v>46234</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H183" s="1" t="s">
         <v>14</v>
@@ -5973,7 +5991,7 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
-        <v>540036</v>
+        <v>541584</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>217</v>
@@ -5982,16 +6000,16 @@
         <v>0</v>
       </c>
       <c r="D184" s="1">
-        <v>218</v>
-      </c>
-      <c r="E184" s="1">
+        <v>43</v>
+      </c>
+      <c r="E184" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F184" s="1">
         <v>46234</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H184" s="1" t="s">
         <v>14</v>
@@ -5999,7 +6017,7 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
-        <v>540014</v>
+        <v>660000</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>218</v>
@@ -6008,24 +6026,24 @@
         <v>0</v>
       </c>
       <c r="D185" s="1">
-        <v>56</v>
-      </c>
-      <c r="E185" s="1">
+        <v>86</v>
+      </c>
+      <c r="E185" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F185" s="1">
         <v>46234</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
-        <v>540035</v>
+        <v>542044</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>219</v>
@@ -6034,16 +6052,16 @@
         <v>0</v>
       </c>
       <c r="D186" s="1">
-        <v>250</v>
-      </c>
-      <c r="E186" s="1">
+        <v>42</v>
+      </c>
+      <c r="E186" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F186" s="1">
         <v>46234</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H186" s="1" t="s">
         <v>14</v>
@@ -6051,7 +6069,7 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
-        <v>541584</v>
+        <v>650202</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>220</v>
@@ -6060,24 +6078,24 @@
         <v>0</v>
       </c>
       <c r="D187" s="1">
-        <v>43</v>
-      </c>
-      <c r="E187" s="1">
+        <v>76</v>
+      </c>
+      <c r="E187" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F187" s="1">
         <v>46234</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
-        <v>660000</v>
+        <v>150006</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>221</v>
@@ -6086,24 +6104,24 @@
         <v>0</v>
       </c>
       <c r="D188" s="1">
-        <v>86</v>
-      </c>
-      <c r="E188" s="1">
+        <v>7.9</v>
+      </c>
+      <c r="E188" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F188" s="1">
         <v>46234</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
-        <v>542044</v>
+        <v>150003</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>222</v>
@@ -6112,16 +6130,16 @@
         <v>0</v>
       </c>
       <c r="D189" s="1">
-        <v>42</v>
-      </c>
-      <c r="E189" s="1">
+        <v>7.55</v>
+      </c>
+      <c r="E189" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F189" s="1">
         <v>46234</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H189" s="1" t="s">
         <v>14</v>
@@ -6129,7 +6147,7 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
-        <v>650202</v>
+        <v>150001</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>223</v>
@@ -6138,24 +6156,24 @@
         <v>0</v>
       </c>
       <c r="D190" s="1">
-        <v>76</v>
-      </c>
-      <c r="E190" s="1">
+        <v>29.9</v>
+      </c>
+      <c r="E190" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F190" s="1">
         <v>46234</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
-        <v>150006</v>
+        <v>150002</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>224</v>
@@ -6164,24 +6182,24 @@
         <v>0</v>
       </c>
       <c r="D191" s="1">
-        <v>7.9</v>
-      </c>
-      <c r="E191" s="1">
+        <v>28.75</v>
+      </c>
+      <c r="E191" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F191" s="1">
         <v>46234</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
-        <v>150003</v>
+        <v>503624</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>225</v>
@@ -6190,24 +6208,24 @@
         <v>0</v>
       </c>
       <c r="D192" s="1">
-        <v>7.55</v>
-      </c>
-      <c r="E192" s="1">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="E192" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F192" s="1">
         <v>46234</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
-        <v>150001</v>
+        <v>535805</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>226</v>
@@ -6216,24 +6234,24 @@
         <v>0</v>
       </c>
       <c r="D193" s="1">
-        <v>29.9</v>
-      </c>
-      <c r="E193" s="1">
+        <v>16</v>
+      </c>
+      <c r="E193" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F193" s="1">
         <v>46234</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
-        <v>150002</v>
+        <v>535801</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>227</v>
@@ -6242,24 +6260,24 @@
         <v>0</v>
       </c>
       <c r="D194" s="1">
-        <v>28.75</v>
-      </c>
-      <c r="E194" s="1">
+        <v>44</v>
+      </c>
+      <c r="E194" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F194" s="1">
         <v>46234</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
-        <v>503624</v>
+        <v>535702</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>228</v>
@@ -6268,24 +6286,24 @@
         <v>0</v>
       </c>
       <c r="D195" s="1">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="E195" s="1">
+        <v>145</v>
+      </c>
+      <c r="E195" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F195" s="1">
         <v>46234</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
-        <v>535805</v>
+        <v>535700</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>229</v>
@@ -6294,16 +6312,16 @@
         <v>0</v>
       </c>
       <c r="D196" s="1">
-        <v>16</v>
-      </c>
-      <c r="E196" s="1">
+        <v>14</v>
+      </c>
+      <c r="E196" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F196" s="1">
         <v>46234</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H196" s="1" t="s">
         <v>31</v>
@@ -6311,7 +6329,7 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
-        <v>535801</v>
+        <v>141407</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>230</v>
@@ -6320,24 +6338,24 @@
         <v>0</v>
       </c>
       <c r="D197" s="1">
-        <v>44</v>
-      </c>
-      <c r="E197" s="1">
+        <v>46</v>
+      </c>
+      <c r="E197" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F197" s="1">
         <v>46234</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
-        <v>535702</v>
+        <v>510304</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>231</v>
@@ -6346,24 +6364,24 @@
         <v>0</v>
       </c>
       <c r="D198" s="1">
-        <v>145</v>
-      </c>
-      <c r="E198" s="1">
+        <v>26.55</v>
+      </c>
+      <c r="E198" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F198" s="1">
         <v>46234</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
-        <v>535700</v>
+        <v>521511</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>232</v>
@@ -6372,16 +6390,16 @@
         <v>0</v>
       </c>
       <c r="D199" s="1">
-        <v>14</v>
-      </c>
-      <c r="E199" s="1">
+        <v>8.35</v>
+      </c>
+      <c r="E199" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F199" s="1">
         <v>46234</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H199" s="1" t="s">
         <v>31</v>
@@ -6389,7 +6407,7 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
-        <v>141407</v>
+        <v>512385</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>233</v>
@@ -6398,24 +6416,24 @@
         <v>0</v>
       </c>
       <c r="D200" s="1">
-        <v>46</v>
-      </c>
-      <c r="E200" s="1">
+        <v>26</v>
+      </c>
+      <c r="E200" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F200" s="1">
         <v>46234</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
-        <v>510304</v>
+        <v>510305</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>234</v>
@@ -6424,16 +6442,16 @@
         <v>0</v>
       </c>
       <c r="D201" s="1">
-        <v>26.55</v>
-      </c>
-      <c r="E201" s="1">
+        <v>15.35</v>
+      </c>
+      <c r="E201" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F201" s="1">
         <v>46234</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H201" s="1" t="s">
         <v>10</v>
@@ -6441,7 +6459,7 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
-        <v>521511</v>
+        <v>510306</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>235</v>
@@ -6450,24 +6468,24 @@
         <v>0</v>
       </c>
       <c r="D202" s="1">
-        <v>8.35</v>
-      </c>
-      <c r="E202" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="E202" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F202" s="1">
         <v>46234</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
-        <v>512385</v>
+        <v>510308</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>236</v>
@@ -6476,16 +6494,16 @@
         <v>0</v>
       </c>
       <c r="D203" s="1">
-        <v>26</v>
-      </c>
-      <c r="E203" s="1">
+        <v>11.16</v>
+      </c>
+      <c r="E203" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F203" s="1">
         <v>46234</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H203" s="1" t="s">
         <v>10</v>
@@ -6493,7 +6511,7 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
-        <v>510305</v>
+        <v>501216</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>237</v>
@@ -6502,16 +6520,16 @@
         <v>0</v>
       </c>
       <c r="D204" s="1">
-        <v>15.35</v>
-      </c>
-      <c r="E204" s="1">
+        <v>115.3</v>
+      </c>
+      <c r="E204" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F204" s="1">
         <v>46234</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H204" s="1" t="s">
         <v>10</v>
@@ -6519,7 +6537,7 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
-        <v>510306</v>
+        <v>503710</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>238</v>
@@ -6528,16 +6546,16 @@
         <v>0</v>
       </c>
       <c r="D205" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="E205" s="1">
+        <v>5.95</v>
+      </c>
+      <c r="E205" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F205" s="1">
         <v>46234</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H205" s="1" t="s">
         <v>10</v>
@@ -6545,7 +6563,7 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
-        <v>510308</v>
+        <v>503709</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>239</v>
@@ -6554,16 +6572,16 @@
         <v>0</v>
       </c>
       <c r="D206" s="1">
-        <v>11.16</v>
-      </c>
-      <c r="E206" s="1">
+        <v>14.91</v>
+      </c>
+      <c r="E206" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F206" s="1">
         <v>46234</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H206" s="1" t="s">
         <v>10</v>
@@ -6571,7 +6589,7 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
-        <v>501216</v>
+        <v>541505</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>240</v>
@@ -6580,24 +6598,24 @@
         <v>0</v>
       </c>
       <c r="D207" s="1">
-        <v>115.3</v>
-      </c>
-      <c r="E207" s="1">
+        <v>127</v>
+      </c>
+      <c r="E207" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F207" s="1">
         <v>46234</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
-        <v>503710</v>
+        <v>141703</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>241</v>
@@ -6606,24 +6624,24 @@
         <v>0</v>
       </c>
       <c r="D208" s="1">
-        <v>5.95</v>
-      </c>
-      <c r="E208" s="1">
+        <v>3</v>
+      </c>
+      <c r="E208" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F208" s="1">
         <v>46234</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
-        <v>503709</v>
+        <v>141702</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>242</v>
@@ -6632,24 +6650,24 @@
         <v>0</v>
       </c>
       <c r="D209" s="1">
-        <v>14.91</v>
-      </c>
-      <c r="E209" s="1">
+        <v>2</v>
+      </c>
+      <c r="E209" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F209" s="1">
         <v>46234</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H209" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
-        <v>541505</v>
+        <v>141707</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>243</v>
@@ -6658,24 +6676,24 @@
         <v>0</v>
       </c>
       <c r="D210" s="1">
-        <v>127</v>
-      </c>
-      <c r="E210" s="1">
+        <v>7.85</v>
+      </c>
+      <c r="E210" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F210" s="1">
         <v>46234</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
-        <v>141703</v>
+        <v>141701</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>244</v>
@@ -6684,16 +6702,16 @@
         <v>0</v>
       </c>
       <c r="D211" s="1">
-        <v>3</v>
-      </c>
-      <c r="E211" s="1">
+        <v>28</v>
+      </c>
+      <c r="E211" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F211" s="1">
         <v>46234</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H211" s="1" t="s">
         <v>14</v>
@@ -6701,7 +6719,7 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
-        <v>141702</v>
+        <v>141704</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>245</v>
@@ -6710,16 +6728,16 @@
         <v>0</v>
       </c>
       <c r="D212" s="1">
-        <v>2</v>
-      </c>
-      <c r="E212" s="1">
+        <v>17</v>
+      </c>
+      <c r="E212" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F212" s="1">
         <v>46234</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H212" s="1" t="s">
         <v>14</v>
@@ -6727,7 +6745,7 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
-        <v>141707</v>
+        <v>141705</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>246</v>
@@ -6736,16 +6754,16 @@
         <v>0</v>
       </c>
       <c r="D213" s="1">
-        <v>7.85</v>
-      </c>
-      <c r="E213" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="E213" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F213" s="1">
         <v>46234</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H213" s="1" t="s">
         <v>10</v>
@@ -6753,7 +6771,7 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
-        <v>141701</v>
+        <v>511229</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>247</v>
@@ -6762,24 +6780,24 @@
         <v>0</v>
       </c>
       <c r="D214" s="1">
-        <v>28</v>
-      </c>
-      <c r="E214" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="E214" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F214" s="1">
         <v>46234</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H214" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
-        <v>141704</v>
+        <v>520006</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>248</v>
@@ -6788,24 +6806,24 @@
         <v>0</v>
       </c>
       <c r="D215" s="1">
-        <v>17</v>
-      </c>
-      <c r="E215" s="1">
+        <v>6.75</v>
+      </c>
+      <c r="E215" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F215" s="1">
         <v>46234</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H215" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
-        <v>141705</v>
+        <v>520005</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>249</v>
@@ -6814,24 +6832,24 @@
         <v>0</v>
       </c>
       <c r="D216" s="1">
-        <v>0.45</v>
-      </c>
-      <c r="E216" s="1">
+        <v>67.25</v>
+      </c>
+      <c r="E216" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F216" s="1">
         <v>46234</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H216" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
-        <v>511229</v>
+        <v>520000</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>250</v>
@@ -6840,24 +6858,24 @@
         <v>0</v>
       </c>
       <c r="D217" s="1">
-        <v>22.5</v>
-      </c>
-      <c r="E217" s="1">
+        <v>17.649999999999999</v>
+      </c>
+      <c r="E217" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F217" s="1">
         <v>46234</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H217" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
-        <v>520006</v>
+        <v>141717</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>251</v>
@@ -6866,24 +6884,24 @@
         <v>0</v>
       </c>
       <c r="D218" s="1">
-        <v>6.75</v>
-      </c>
-      <c r="E218" s="1">
+        <v>29.6</v>
+      </c>
+      <c r="E218" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F218" s="1">
         <v>46234</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
-        <v>520005</v>
+        <v>210007</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>252</v>
@@ -6892,24 +6910,24 @@
         <v>0</v>
       </c>
       <c r="D219" s="1">
-        <v>67.25</v>
-      </c>
-      <c r="E219" s="1">
+        <v>18</v>
+      </c>
+      <c r="E219" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F219" s="1">
         <v>46234</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
-        <v>520000</v>
+        <v>210006</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>253</v>
@@ -6918,24 +6936,24 @@
         <v>0</v>
       </c>
       <c r="D220" s="1">
-        <v>17.649999999999999</v>
-      </c>
-      <c r="E220" s="1">
+        <v>38</v>
+      </c>
+      <c r="E220" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F220" s="1">
         <v>46234</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H220" s="1" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
-        <v>141717</v>
+        <v>210005</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>254</v>
@@ -6944,24 +6962,24 @@
         <v>0</v>
       </c>
       <c r="D221" s="1">
-        <v>29.6</v>
-      </c>
-      <c r="E221" s="1">
+        <v>29</v>
+      </c>
+      <c r="E221" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F221" s="1">
         <v>46234</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H221" s="1" t="s">
-        <v>10</v>
+        <v>83</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
-        <v>210007</v>
+        <v>523305</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>255</v>
@@ -6970,24 +6988,24 @@
         <v>0</v>
       </c>
       <c r="D222" s="1">
-        <v>18</v>
-      </c>
-      <c r="E222" s="1">
+        <v>148</v>
+      </c>
+      <c r="E222" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F222" s="1">
         <v>46234</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H222" s="1" t="s">
-        <v>84</v>
+        <v>31</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
-        <v>210006</v>
+        <v>534808</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>256</v>
@@ -6996,24 +7014,24 @@
         <v>0</v>
       </c>
       <c r="D223" s="1">
-        <v>38</v>
-      </c>
-      <c r="E223" s="1">
+        <v>164</v>
+      </c>
+      <c r="E223" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F223" s="1">
         <v>46234</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H223" s="1" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
-        <v>210005</v>
+        <v>534806</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>257</v>
@@ -7022,24 +7040,24 @@
         <v>0</v>
       </c>
       <c r="D224" s="1">
-        <v>29</v>
-      </c>
-      <c r="E224" s="1">
+        <v>116</v>
+      </c>
+      <c r="E224" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F224" s="1">
         <v>46234</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
-        <v>523302</v>
+        <v>534542</v>
       </c>
       <c r="B225" s="1" t="s">
         <v>258</v>
@@ -7048,16 +7066,16 @@
         <v>0</v>
       </c>
       <c r="D225" s="1">
-        <v>-0.1</v>
-      </c>
-      <c r="E225" s="1">
+        <v>116</v>
+      </c>
+      <c r="E225" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F225" s="1">
         <v>46234</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H225" s="1" t="s">
         <v>31</v>
@@ -7065,7 +7083,7 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
-        <v>523305</v>
+        <v>534213</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>259</v>
@@ -7074,16 +7092,16 @@
         <v>0</v>
       </c>
       <c r="D226" s="1">
-        <v>148</v>
-      </c>
-      <c r="E226" s="1">
+        <v>9.4949999999999992</v>
+      </c>
+      <c r="E226" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F226" s="1">
         <v>46234</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H226" s="1" t="s">
         <v>31</v>
@@ -7091,7 +7109,7 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
-        <v>534808</v>
+        <v>534202</v>
       </c>
       <c r="B227" s="1" t="s">
         <v>260</v>
@@ -7100,24 +7118,24 @@
         <v>0</v>
       </c>
       <c r="D227" s="1">
-        <v>164</v>
-      </c>
-      <c r="E227" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="E227" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F227" s="1">
         <v>46234</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H227" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
-        <v>534806</v>
+        <v>534203</v>
       </c>
       <c r="B228" s="1" t="s">
         <v>261</v>
@@ -7126,24 +7144,24 @@
         <v>0</v>
       </c>
       <c r="D228" s="1">
-        <v>116</v>
-      </c>
-      <c r="E228" s="1">
+        <v>827.2</v>
+      </c>
+      <c r="E228" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F228" s="1">
         <v>46234</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H228" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
-        <v>534542</v>
+        <v>541620</v>
       </c>
       <c r="B229" s="1" t="s">
         <v>262</v>
@@ -7152,24 +7170,24 @@
         <v>0</v>
       </c>
       <c r="D229" s="1">
-        <v>116</v>
-      </c>
-      <c r="E229" s="1">
+        <v>89</v>
+      </c>
+      <c r="E229" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F229" s="1">
         <v>46234</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
-        <v>534213</v>
+        <v>541622</v>
       </c>
       <c r="B230" s="1" t="s">
         <v>263</v>
@@ -7178,24 +7196,24 @@
         <v>0</v>
       </c>
       <c r="D230" s="1">
-        <v>9.4949999999999992</v>
-      </c>
-      <c r="E230" s="1">
+        <v>90</v>
+      </c>
+      <c r="E230" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F230" s="1">
         <v>46234</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
-        <v>534202</v>
+        <v>542036</v>
       </c>
       <c r="B231" s="1" t="s">
         <v>264</v>
@@ -7204,24 +7222,24 @@
         <v>0</v>
       </c>
       <c r="D231" s="1">
-        <v>0.45</v>
-      </c>
-      <c r="E231" s="1">
+        <v>98</v>
+      </c>
+      <c r="E231" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F231" s="1">
         <v>46234</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
-        <v>534203</v>
+        <v>141607</v>
       </c>
       <c r="B232" s="1" t="s">
         <v>265</v>
@@ -7230,24 +7248,24 @@
         <v>0</v>
       </c>
       <c r="D232" s="1">
-        <v>827.2</v>
-      </c>
-      <c r="E232" s="1">
+        <v>53</v>
+      </c>
+      <c r="E232" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F232" s="1">
         <v>46234</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H232" s="1" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
-        <v>541620</v>
+        <v>141406</v>
       </c>
       <c r="B233" s="1" t="s">
         <v>266</v>
@@ -7256,24 +7274,24 @@
         <v>0</v>
       </c>
       <c r="D233" s="1">
-        <v>89</v>
-      </c>
-      <c r="E233" s="1">
+        <v>37</v>
+      </c>
+      <c r="E233" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F233" s="1">
         <v>46234</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
-        <v>541622</v>
+        <v>141110</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>267</v>
@@ -7282,24 +7300,24 @@
         <v>0</v>
       </c>
       <c r="D234" s="1">
-        <v>90</v>
-      </c>
-      <c r="E234" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="E234" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F234" s="1">
         <v>46234</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H234" s="1" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
-        <v>542036</v>
+        <v>541533</v>
       </c>
       <c r="B235" s="1" t="s">
         <v>268</v>
@@ -7308,16 +7326,16 @@
         <v>0</v>
       </c>
       <c r="D235" s="1">
-        <v>98</v>
-      </c>
-      <c r="E235" s="1">
+        <v>238</v>
+      </c>
+      <c r="E235" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F235" s="1">
         <v>46234</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H235" s="1" t="s">
         <v>14</v>
@@ -7325,7 +7343,7 @@
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
-        <v>141607</v>
+        <v>541617</v>
       </c>
       <c r="B236" s="1" t="s">
         <v>269</v>
@@ -7334,24 +7352,24 @@
         <v>0</v>
       </c>
       <c r="D236" s="1">
-        <v>53</v>
-      </c>
-      <c r="E236" s="1">
+        <v>99</v>
+      </c>
+      <c r="E236" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F236" s="1">
         <v>46234</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H236" s="1" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
-        <v>141406</v>
+        <v>511228</v>
       </c>
       <c r="B237" s="1" t="s">
         <v>270</v>
@@ -7360,24 +7378,24 @@
         <v>0</v>
       </c>
       <c r="D237" s="1">
-        <v>37</v>
-      </c>
-      <c r="E237" s="1">
+        <v>26.4</v>
+      </c>
+      <c r="E237" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F237" s="1">
         <v>46234</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H237" s="1" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
-        <v>141110</v>
+        <v>521527</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>271</v>
@@ -7386,24 +7404,24 @@
         <v>0</v>
       </c>
       <c r="D238" s="1">
-        <v>0.9</v>
-      </c>
-      <c r="E238" s="1">
+        <v>94.1</v>
+      </c>
+      <c r="E238" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F238" s="1">
         <v>46234</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H238" s="1" t="s">
-        <v>84</v>
+        <v>31</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
-        <v>541533</v>
+        <v>521817</v>
       </c>
       <c r="B239" s="1" t="s">
         <v>272</v>
@@ -7412,24 +7430,24 @@
         <v>0</v>
       </c>
       <c r="D239" s="1">
-        <v>238</v>
-      </c>
-      <c r="E239" s="1">
+        <v>4</v>
+      </c>
+      <c r="E239" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F239" s="1">
         <v>46234</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H239" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
-        <v>541617</v>
+        <v>521818</v>
       </c>
       <c r="B240" s="1" t="s">
         <v>273</v>
@@ -7438,24 +7456,24 @@
         <v>0</v>
       </c>
       <c r="D240" s="1">
-        <v>99</v>
-      </c>
-      <c r="E240" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="E240" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F240" s="1">
         <v>46234</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H240" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
-        <v>511228</v>
+        <v>521806</v>
       </c>
       <c r="B241" s="1" t="s">
         <v>274</v>
@@ -7464,24 +7482,24 @@
         <v>0</v>
       </c>
       <c r="D241" s="1">
-        <v>26.4</v>
-      </c>
-      <c r="E241" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="E241" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F241" s="1">
         <v>46234</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H241" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
-        <v>521527</v>
+        <v>521802</v>
       </c>
       <c r="B242" s="1" t="s">
         <v>275</v>
@@ -7490,16 +7508,16 @@
         <v>0</v>
       </c>
       <c r="D242" s="1">
-        <v>94.1</v>
-      </c>
-      <c r="E242" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="E242" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F242" s="1">
         <v>46234</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H242" s="1" t="s">
         <v>31</v>
@@ -7507,7 +7525,7 @@
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
-        <v>521817</v>
+        <v>512364</v>
       </c>
       <c r="B243" s="1" t="s">
         <v>276</v>
@@ -7516,24 +7534,24 @@
         <v>0</v>
       </c>
       <c r="D243" s="1">
-        <v>4</v>
-      </c>
-      <c r="E243" s="1">
+        <v>14.65</v>
+      </c>
+      <c r="E243" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F243" s="1">
         <v>46234</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H243" s="1" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
-        <v>521818</v>
+        <v>141404</v>
       </c>
       <c r="B244" s="1" t="s">
         <v>277</v>
@@ -7542,24 +7560,24 @@
         <v>0</v>
       </c>
       <c r="D244" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="E244" s="1">
+        <v>26</v>
+      </c>
+      <c r="E244" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F244" s="1">
         <v>46234</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H244" s="1" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
-        <v>521806</v>
+        <v>141405</v>
       </c>
       <c r="B245" s="1" t="s">
         <v>278</v>
@@ -7568,24 +7586,24 @@
         <v>0</v>
       </c>
       <c r="D245" s="1">
-        <v>7.3</v>
-      </c>
-      <c r="E245" s="1">
+        <v>110</v>
+      </c>
+      <c r="E245" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F245" s="1">
         <v>46234</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H245" s="1" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
-        <v>521802</v>
+        <v>320002</v>
       </c>
       <c r="B246" s="1" t="s">
         <v>279</v>
@@ -7594,24 +7612,24 @@
         <v>0</v>
       </c>
       <c r="D246" s="1">
-        <v>0.09</v>
-      </c>
-      <c r="E246" s="1">
+        <v>97</v>
+      </c>
+      <c r="E246" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F246" s="1">
         <v>46234</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H246" s="1" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
-        <v>512364</v>
+        <v>320003</v>
       </c>
       <c r="B247" s="1" t="s">
         <v>280</v>
@@ -7620,24 +7638,24 @@
         <v>0</v>
       </c>
       <c r="D247" s="1">
-        <v>14.65</v>
-      </c>
-      <c r="E247" s="1">
+        <v>12</v>
+      </c>
+      <c r="E247" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F247" s="1">
         <v>46234</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H247" s="1" t="s">
-        <v>10</v>
+        <v>83</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
-        <v>141404</v>
+        <v>320001</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>281</v>
@@ -7646,126 +7664,23 @@
         <v>0</v>
       </c>
       <c r="D248" s="1">
-        <v>26</v>
-      </c>
-      <c r="E248" s="1">
+        <v>157</v>
+      </c>
+      <c r="E248" s="2">
         <v>46234.602418981478</v>
       </c>
       <c r="F248" s="1">
         <v>46234</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H248" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A249" s="1">
-        <v>141405</v>
-      </c>
-      <c r="B249" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C249" s="1">
-        <v>0</v>
-      </c>
-      <c r="D249" s="1">
-        <v>110</v>
-      </c>
-      <c r="E249" s="1">
-        <v>46234.602418981478</v>
-      </c>
-      <c r="F249" s="1">
-        <v>46234</v>
-      </c>
-      <c r="G249" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H249" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A250" s="1">
-        <v>320002</v>
-      </c>
-      <c r="B250" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C250" s="1">
-        <v>0</v>
-      </c>
-      <c r="D250" s="1">
-        <v>97</v>
-      </c>
-      <c r="E250" s="1">
-        <v>46234.602418981478</v>
-      </c>
-      <c r="F250" s="1">
-        <v>46234</v>
-      </c>
-      <c r="G250" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H250" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A251" s="1">
-        <v>320003</v>
-      </c>
-      <c r="B251" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="C251" s="1">
-        <v>0</v>
-      </c>
-      <c r="D251" s="1">
-        <v>12</v>
-      </c>
-      <c r="E251" s="1">
-        <v>46234.602418981478</v>
-      </c>
-      <c r="F251" s="1">
-        <v>46234</v>
-      </c>
-      <c r="G251" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H251" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A252" s="1">
-        <v>320001</v>
-      </c>
-      <c r="B252" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="C252" s="1">
-        <v>0</v>
-      </c>
-      <c r="D252" s="1">
-        <v>157</v>
-      </c>
-      <c r="E252" s="1">
-        <v>46234.602418981478</v>
-      </c>
-      <c r="F252" s="1">
-        <v>46234</v>
-      </c>
-      <c r="G252" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H252" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H248"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>